--- a/greenfood/testcases/Test_Cases_GreenFood_Duong.xlsx
+++ b/greenfood/testcases/Test_Cases_GreenFood_Duong.xlsx
@@ -8,14 +8,15 @@
     <sheet sheetId="2" name="Thanh Toán" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Bản Đồ GIS" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Theo Dõi Giao Hàng" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Kết quả tổng hợp" state="visible" r:id="rId8"/>
+    <sheet sheetId="5" name="API Backend" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Kết quả tổng hợp" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="813">
   <si>
     <t>Tên chức năng</t>
   </si>
@@ -65,17 +66,17 @@
     <t>Shipping_List</t>
   </si>
   <si>
-    <t>Kiểm tra giao diện trang Quản Lý Phí Giao Hàng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Truy cập trang Phí Giao Hàng
-2. Quan sát bảng</t>
+    <t>Kiểm tra tải trang Quản Lý Phí Giao Hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Truy cập /admin/shipping
+2. Quan sát giao diện</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Hiển thị tiêu đề, ô tìm kiếm, nút "Thêm vùng mới", bảng danh sách các vùng giao hàng</t>
+    <t>Hiển thị tiêu đề "Quản lý Phí Giao Hàng", ô tìm kiếm, nút "Thêm vùng mới", bảng danh sách các vùng</t>
   </si>
   <si>
     <t>High</t>
@@ -87,100 +88,158 @@
     <t>TC_SHIP_002</t>
   </si>
   <si>
-    <t>Shipping_Search</t>
-  </si>
-  <si>
-    <t>Tìm kiếm vùng giao hàng với từ khóa hợp lệ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Nhập tên vùng hoặc tỉnh thành
-2. Quan sát kết quả</t>
+    <t>Shipping_List_Data</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị dữ liệu bảng vùng giao hàng</t>
+  </si>
+  <si>
+    <t>1. Xem các cột trong bảng</t>
+  </si>
+  <si>
+    <t>Bảng có đủ cột: Mã, Tên vùng, Phí cơ bản, Phí/kg thêm, Miễn phí từ, Thời gian, Trạng thái, Thao tác</t>
+  </si>
+  <si>
+    <t>TC_SHIP_003</t>
+  </si>
+  <si>
+    <t>Shipping_Search_Name</t>
+  </si>
+  <si>
+    <t>Tìm kiếm vùng theo tên vùng hợp lệ</t>
+  </si>
+  <si>
+    <t>1. Nhập tên vùng vào ô tìm kiếm</t>
   </si>
   <si>
     <t>Từ khóa: "TP.HCM"</t>
   </si>
   <si>
-    <t>Danh sách chỉ hiển thị các vùng có chứa từ khóa</t>
-  </si>
-  <si>
-    <t>TC_SHIP_003</t>
-  </si>
-  <si>
-    <t>Tìm kiếm không có kết quả</t>
-  </si>
-  <si>
-    <t>1. Nhập từ khóa không tồn tại</t>
+    <t>Bảng chỉ hiển thị các vùng có tên chứa "TP.HCM" (Nội thành, Ngoại thành)</t>
+  </si>
+  <si>
+    <t>TC_SHIP_004</t>
+  </si>
+  <si>
+    <t>Shipping_Search_Province</t>
+  </si>
+  <si>
+    <t>Tìm kiếm vùng theo tên Tỉnh/Thành</t>
+  </si>
+  <si>
+    <t>1. Nhập tên tỉnh vào ô tìm kiếm</t>
+  </si>
+  <si>
+    <t>Từ khóa: "Bến Tre"</t>
+  </si>
+  <si>
+    <t>Hiển thị vùng "Đồng Bằng Sông Cửu Long"</t>
+  </si>
+  <si>
+    <t>TC_SHIP_005</t>
+  </si>
+  <si>
+    <t>Shipping_Search_NoResult</t>
+  </si>
+  <si>
+    <t>Tìm kiếm với từ khóa không tồn tại</t>
+  </si>
+  <si>
+    <t>1. Nhập từ khóa không có trong hệ thống</t>
   </si>
   <si>
     <t>Từ khóa: "XYZ999"</t>
   </si>
   <si>
-    <t>Bảng hiển thị trạng thái "Không tìm thấy vùng giao hàng nào!"</t>
+    <t>Bảng hiển thị thông báo "Không tìm thấy vùng giao hàng nào!"</t>
   </si>
   <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>TC_SHIP_004</t>
-  </si>
-  <si>
-    <t>Tìm kiếm với khoảng trắng đầu/cuối</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Nhập từ khóa có khoảng trắng
-2. Quan sát</t>
-  </si>
-  <si>
-    <t>Từ khóa: "   Miền Bắc   "</t>
-  </si>
-  <si>
-    <t>Hệ thống tự trim() và hiển thị kết quả đúng</t>
+    <t>TC_SHIP_006</t>
+  </si>
+  <si>
+    <t>Shipping_Search_Case</t>
+  </si>
+  <si>
+    <t>Tìm kiếm không phân biệt chữ hoa/thường</t>
+  </si>
+  <si>
+    <t>1. Nhập "miền bắc" hoặc "MIỀN BẮC"</t>
+  </si>
+  <si>
+    <t>Từ khóa: "miền bắc"</t>
+  </si>
+  <si>
+    <t>Đều trả về kết quả vùng "Miền Bắc"</t>
+  </si>
+  <si>
+    <t>TC_SHIP_007</t>
+  </si>
+  <si>
+    <t>Shipping_Search_Trim</t>
+  </si>
+  <si>
+    <t>Tìm kiếm có khoảng trắng đầu/cuối</t>
+  </si>
+  <si>
+    <t>1. Nhập từ khóa có space đầu cuối</t>
+  </si>
+  <si>
+    <t>Từ khóa: "   Tây Nguyên   "</t>
+  </si>
+  <si>
+    <t>Hệ thống tự trim khoảng trắng và hiển thị kết quả đúng</t>
   </si>
   <si>
     <t>Low</t>
   </si>
   <si>
-    <t>TC_SHIP_005</t>
+    <t>TC_SHIP_008</t>
+  </si>
+  <si>
+    <t>Shipping_Search_SpecialChar</t>
   </si>
   <si>
     <t>Tìm kiếm với ký tự đặc biệt</t>
   </si>
   <si>
-    <t>1. Nhập ký tự đặc biệt vào ô tìm kiếm</t>
-  </si>
-  <si>
-    <t>Từ khóa: "!@#$%"</t>
-  </si>
-  <si>
-    <t>Không lỗi hệ thống, trả về danh sách trống hoặc kết quả phù hợp</t>
-  </si>
-  <si>
-    <t>TC_SHIP_006</t>
+    <t>1. Nhập ký tự đặc biệt vào ô search</t>
+  </si>
+  <si>
+    <t>Từ khóa: "!@#$%^&amp;*"</t>
+  </si>
+  <si>
+    <t>Hệ thống xử lý an toàn, không lỗi crash màn hình, hiển thị danh sách trống</t>
+  </si>
+  <si>
+    <t>TC_SHIP_009</t>
   </si>
   <si>
     <t>Shipping_Add_UI</t>
   </si>
   <si>
-    <t>Kiểm tra giao diện popup Thêm vùng giao hàng</t>
+    <t>Kiểm tra mở Popup Thêm vùng giao hàng</t>
   </si>
   <si>
     <t>1. Nhấn nút "Thêm vùng mới"</t>
   </si>
   <si>
-    <t>Popup hiển thị các trường: Tên vùng, Tỉnh/thành, Phí cơ bản, Phí/kg thêm, Miễn phí từ, Thời gian giao, Kích hoạt; có nút Lưu và Hủy</t>
-  </si>
-  <si>
-    <t>TC_SHIP_007</t>
-  </si>
-  <si>
-    <t>Shipping_Add_Name</t>
-  </si>
-  <si>
-    <t>Để trống Tên vùng giao hàng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Để trống Tên vùng
-2. Điền đủ các trường khác
+    <t>Popup mở ra với tiêu đề "Thêm vùng giao hàng mới", các ô input trống, nút Lưu &amp; Hủy</t>
+  </si>
+  <si>
+    <t>TC_SHIP_010</t>
+  </si>
+  <si>
+    <t>Shipping_Add_EmptyName</t>
+  </si>
+  <si>
+    <t>Thêm vùng - Bỏ trống Tên vùng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Bỏ trống Tên vùng
+2. Điền các trường khác
 3. Bấm Lưu</t>
   </si>
   <si>
@@ -190,18 +249,17 @@
     <t>Báo lỗi "Tên vùng giao hàng không được để trống!"</t>
   </si>
   <si>
-    <t>TC_SHIP_008</t>
-  </si>
-  <si>
-    <t>Shipping_Add_Provinces</t>
-  </si>
-  <si>
-    <t>Để trống danh sách Tỉnh/Thành phố</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Nhập tên vùng
-2. Để trống Tỉnh/Thành
-3. Bấm Lưu</t>
+    <t>TC_SHIP_011</t>
+  </si>
+  <si>
+    <t>Shipping_Add_EmptyProvinces</t>
+  </si>
+  <si>
+    <t>Thêm vùng - Bỏ trống danh sách Tỉnh/Thành</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Điền Tên, bỏ trống Tỉnh/Thành
+2. Bấm Lưu</t>
   </si>
   <si>
     <t>Tỉnh/Thành: (Empty)</t>
@@ -210,73 +268,73 @@
     <t>Báo lỗi "Danh sách tỉnh/thành không được để trống!"</t>
   </si>
   <si>
-    <t>TC_SHIP_009</t>
-  </si>
-  <si>
-    <t>Shipping_Add_Fee</t>
-  </si>
-  <si>
-    <t>Nhập Phí cơ bản là số âm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Nhập Phí cơ bản: -20000
+    <t>TC_SHIP_012</t>
+  </si>
+  <si>
+    <t>Shipping_Add_NegativeBaseFee</t>
+  </si>
+  <si>
+    <t>Thêm vùng - Nhập Phí cơ bản là số âm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập Phí cơ bản = -15000
 2. Bấm Lưu</t>
   </si>
   <si>
-    <t>Phí cơ bản: -20000</t>
-  </si>
-  <si>
-    <t>Hệ thống chặn, báo lỗi "Phí cơ bản không được âm!"</t>
-  </si>
-  <si>
-    <t>TC_SHIP_010</t>
-  </si>
-  <si>
-    <t>Shipping_Add_ExtraFee</t>
-  </si>
-  <si>
-    <t>Nhập Phí mỗi kg thêm là số âm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Nhập Phí mỗi kg thêm: -5000
+    <t>Phí cơ bản: -15000</t>
+  </si>
+  <si>
+    <t>Báo lỗi "Phí cơ bản không được âm!"</t>
+  </si>
+  <si>
+    <t>TC_SHIP_013</t>
+  </si>
+  <si>
+    <t>Shipping_Add_NegativeExtraFee</t>
+  </si>
+  <si>
+    <t>Thêm vùng - Nhập Phí mỗi kg thêm là số âm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập Phí/kg = -5000
 2. Bấm Lưu</t>
   </si>
   <si>
-    <t>Phí/kg thêm: -5000</t>
-  </si>
-  <si>
-    <t>Hệ thống chặn, báo lỗi "Phí mỗi kg thêm không được âm!"</t>
-  </si>
-  <si>
-    <t>TC_SHIP_011</t>
-  </si>
-  <si>
-    <t>Shipping_Add_FreeMin</t>
-  </si>
-  <si>
-    <t>Nhập Mức miễn phí ship là số âm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Nhập Mức miễn phí: -300000
+    <t>Phí/kg: -5000</t>
+  </si>
+  <si>
+    <t>Báo lỗi "Phí mỗi kg thêm không được âm!"</t>
+  </si>
+  <si>
+    <t>TC_SHIP_014</t>
+  </si>
+  <si>
+    <t>Shipping_Add_NegativeFreeMin</t>
+  </si>
+  <si>
+    <t>Thêm vùng - Nhập Mức miễn phí ship là số âm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập Miễn phí từ = -300000
 2. Bấm Lưu</t>
   </si>
   <si>
     <t>Miễn phí từ: -300000</t>
   </si>
   <si>
-    <t>Hệ thống chặn, báo lỗi "Mức miễn phí ship không được âm!"</t>
-  </si>
-  <si>
-    <t>TC_SHIP_012</t>
-  </si>
-  <si>
-    <t>Shipping_Add_Time</t>
-  </si>
-  <si>
-    <t>Để trống Thời gian giao hàng dự kiến</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Để trống trường thời gian giao
+    <t>Báo lỗi "Mức miễn phí ship không được âm!"</t>
+  </si>
+  <si>
+    <t>TC_SHIP_015</t>
+  </si>
+  <si>
+    <t>Shipping_Add_EmptyDays</t>
+  </si>
+  <si>
+    <t>Thêm vùng - Bỏ trống Thời gian giao dự kiến</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Bỏ trống Thời gian giao
 2. Bấm Lưu</t>
   </si>
   <si>
@@ -286,166 +344,318 @@
     <t>Báo lỗi "Thời gian giao hàng dự kiến không được để trống!"</t>
   </si>
   <si>
-    <t>TC_SHIP_013</t>
+    <t>TC_SHIP_016</t>
   </si>
   <si>
     <t>Shipping_Add_Valid</t>
   </si>
   <si>
-    <t>Thêm vùng giao hàng thành công</t>
+    <t>Thêm vùng giao hàng hợp lệ thành công</t>
   </si>
   <si>
     <t xml:space="preserve">1. Điền đầy đủ thông tin chuẩn
-2. Nhấn Lưu</t>
+2. Bấm "Thêm mới"</t>
   </si>
   <si>
     <t>Tên: Vùng Đông Bắc, Tỉnh: Quảng Ninh, Phí: 45000, TG: 2-3 ngày</t>
   </si>
   <si>
-    <t>Lưu thành công, thông báo toast xanh, popup đóng, bản ghi mới hiện trên danh sách</t>
-  </si>
-  <si>
-    <t>TC_SHIP_014</t>
-  </si>
-  <si>
-    <t>Shipping_Add_MultiClick</t>
-  </si>
-  <si>
-    <t>Nhấn Lưu nhiều lần liên tiếp (Rapid click)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Điền đủ thông tin
-2. Nhấn đúp thật nhanh nút Lưu</t>
-  </si>
-  <si>
-    <t>Dữ liệu hợp lệ</t>
-  </si>
-  <si>
-    <t>Chỉ tạo ra 1 bản ghi duy nhất, nút lưu hiển thị "Đang lưu..." và disabled</t>
-  </si>
-  <si>
-    <t>TC_SHIP_015</t>
+    <t>Toast thông báo thành công, dữ liệu lưu vào CSDL, bản ghi mới hiện ở bảng</t>
+  </si>
+  <si>
+    <t>TC_SHIP_017</t>
+  </si>
+  <si>
+    <t>Shipping_Add_ZeroFee</t>
+  </si>
+  <si>
+    <t>Thêm vùng giao hàng với Phí cơ bản = 0đ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập Phí cơ bản = 0đ (Vùng ưu đãi)
+2. Bấm Lưu</t>
+  </si>
+  <si>
+    <t>Phí cơ bản: 0đ</t>
+  </si>
+  <si>
+    <t>Chấp nhận 0đ, hiển thị 0đ trong bảng</t>
+  </si>
+  <si>
+    <t>TC_SHIP_018</t>
+  </si>
+  <si>
+    <t>Shipping_Add_RapidClick</t>
+  </si>
+  <si>
+    <t>Nhấn nút Lưu nhiều lần liên tiếp (Rapid Click)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Điền thông tin chuẩn
+2. Click đúp thật nhanh nút Lưu</t>
+  </si>
+  <si>
+    <t>Dữ liệu chuẩn</t>
+  </si>
+  <si>
+    <t>Nút chuyển sang "Đang lưu...", disabled, chỉ tạo duy nhất 1 bản ghi</t>
+  </si>
+  <si>
+    <t>TC_SHIP_019</t>
   </si>
   <si>
     <t>Shipping_Add_Cancel</t>
   </si>
   <si>
-    <t>Nhấn nút Hủy / icon Đóng popup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Mở popup, nhập dữ liệu dở dang
-2. Nhấn Hủy hoặc X</t>
-  </si>
-  <si>
-    <t>Data nhập dở dang</t>
-  </si>
-  <si>
-    <t>Popup đóng, không lưu dữ liệu mới vào bảng</t>
-  </si>
-  <si>
-    <t>TC_SHIP_016</t>
+    <t>Hủy thêm vùng giao hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Mở popup, điền dở dang
+2. Bấm nút "Hủy" hoặc X</t>
+  </si>
+  <si>
+    <t>Dữ liệu dở dang</t>
+  </si>
+  <si>
+    <t>Popup đóng, không có bản ghi mới nào được lưu</t>
+  </si>
+  <si>
+    <t>TC_SHIP_020</t>
   </si>
   <si>
     <t>Shipping_Edit_UI</t>
   </si>
   <si>
-    <t>Kiểm tra popup Chỉnh Sửa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Chọn vùng giao hàng bất kỳ
-2. Nhấn icon Bút chì (Sửa)</t>
-  </si>
-  <si>
-    <t>Dữ liệu hiện tại của vùng được đổ đầy đủ vào các ô input</t>
-  </si>
-  <si>
-    <t>TC_SHIP_017</t>
+    <t>Kiểm tra mở Popup Chỉnh sửa vùng giao hàng</t>
+  </si>
+  <si>
+    <t>1. Nhấn icon Bút chì tại 1 dòng bất kỳ</t>
+  </si>
+  <si>
+    <t>SZ001</t>
+  </si>
+  <si>
+    <t>Popup mở với tiêu đề "Chỉnh sửa: [Tên vùng]", dữ liệu cũ được điền sẵn đầy đủ</t>
+  </si>
+  <si>
+    <t>TC_SHIP_021</t>
   </si>
   <si>
     <t>Shipping_Edit_Valid</t>
   </si>
   <si>
-    <t>Cập nhật phí giao hàng thành công</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Sửa Phí cơ bản và Thời gian giao
-2. Nhấn Cập nhật</t>
-  </si>
-  <si>
-    <t>Phí mới: 25000đ, TG: 1-2 ngày</t>
-  </si>
-  <si>
-    <t>Cập nhật thành công, toast thông báo, bảng cập nhật giá trị mới</t>
-  </si>
-  <si>
-    <t>TC_SHIP_018</t>
-  </si>
-  <si>
-    <t>Shipping_Edit_Status</t>
-  </si>
-  <si>
-    <t>Chuyển đổi trạng thái Hoạt động / Tạm ngưng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Bỏ tick "Kích hoạt"
-2. Nhấn Cập nhật</t>
-  </si>
-  <si>
-    <t>Kích hoạt: false</t>
-  </si>
-  <si>
-    <t>Trạng thái chuyển sang badge xám "Tạm ngưng"</t>
-  </si>
-  <si>
-    <t>TC_SHIP_019</t>
+    <t>Cập nhật thay đổi Phí và Thời gian giao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Đổi Phí cơ bản = 20000, TG = 1 ngày
+2. Bấm "Cập nhật"</t>
+  </si>
+  <si>
+    <t>Phí: 20000, TG: 1 ngày</t>
+  </si>
+  <si>
+    <t>Toast thông báo thành công, bảng cập nhật giá trị mới lập tức</t>
+  </si>
+  <si>
+    <t>TC_SHIP_022</t>
+  </si>
+  <si>
+    <t>Shipping_Edit_StatusActive</t>
+  </si>
+  <si>
+    <t>Chuyển đổi trạng thái từ Hoạt động sang Tạm ngưng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Mở sửa
+2. Bỏ tick checkbox "Kích hoạt"
+3. Bấm Cập nhật</t>
+  </si>
+  <si>
+    <t>is_active: false</t>
+  </si>
+  <si>
+    <t>Badge trạng thái chuyển từ "Hoạt động" (xanh) sang "Tạm ngưng" (xám)</t>
+  </si>
+  <si>
+    <t>TC_SHIP_023</t>
+  </si>
+  <si>
+    <t>Shipping_Edit_Cancel</t>
+  </si>
+  <si>
+    <t>Hủy chỉnh sửa vùng giao hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Sửa dữ liệu trong form
+2. Bấm nút "Hủy"</t>
+  </si>
+  <si>
+    <t>Data mới</t>
+  </si>
+  <si>
+    <t>Popup đóng, dữ liệu cũ giữ nguyên không bị thay đổi</t>
+  </si>
+  <si>
+    <t>TC_SHIP_024</t>
   </si>
   <si>
     <t>Shipping_Del_UI</t>
   </si>
   <si>
-    <t>Kiểm tra popup Xóa vùng giao hàng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Nhấn icon Thùng rác (Xóa)
-2. Quan sát</t>
-  </si>
-  <si>
-    <t>Hiển thị cảnh báo xác nhận xóa đúng tên vùng cần xóa</t>
-  </si>
-  <si>
-    <t>TC_SHIP_020</t>
+    <t>Kiểm tra Popup xác nhận Xóa vùng giao hàng</t>
+  </si>
+  <si>
+    <t>1. Nhấn icon Thùng rác (Xóa)</t>
+  </si>
+  <si>
+    <t>Vùng SZ001</t>
+  </si>
+  <si>
+    <t>Popup xác nhận hiển thị cảnh báo, nêu rõ tên vùng sắp xóa kèm nút Xóa/Hủy</t>
+  </si>
+  <si>
+    <t>TC_SHIP_025</t>
   </si>
   <si>
     <t>Shipping_Del_Confirm</t>
   </si>
   <si>
-    <t>Xác nhận Xóa vùng giao hàng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Nhấn Xóa
-2. Nhấn nút "Xóa" trên modal xác nhận</t>
+    <t>Xác nhận Xóa vùng giao hàng thành công</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Mở popup xóa
+2. Nhấn nút "Xóa"</t>
   </si>
   <si>
     <t>Vùng đã chọn</t>
   </si>
   <si>
-    <t>Bản ghi biến mất khỏi danh sách, báo thành công</t>
-  </si>
-  <si>
-    <t>TC_SHIP_021</t>
+    <t>Bản ghi bị xóa khỏi CSDL, biến mất khỏi bảng, toast thông báo thành công</t>
+  </si>
+  <si>
+    <t>TC_SHIP_026</t>
   </si>
   <si>
     <t>Shipping_Del_Cancel</t>
   </si>
   <si>
-    <t>Hủy xóa vùng giao hàng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Nhấn Xóa
+    <t>Hủy xác nhận Xóa vùng giao hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Mở popup xóa
 2. Nhấn nút "Hủy"</t>
   </si>
   <si>
-    <t>Đóng popup xác nhận, bản ghi vẫn còn nguyên vẹn trong danh sách</t>
+    <t>Popup đóng, bản ghi vẫn còn nguyên vẹn trong bảng</t>
+  </si>
+  <si>
+    <t>TC_SHIP_027</t>
+  </si>
+  <si>
+    <t>Shipping_Currency_Format</t>
+  </si>
+  <si>
+    <t>Kiểm tra định dạng tiền tệ trên bảng</t>
+  </si>
+  <si>
+    <t>1. Quan sát các cột phí trong bảng</t>
+  </si>
+  <si>
+    <t>Tất cả các khoản tiền hiển thị đúng chuẩn VNĐ có dấu phân cách hàng nghìn (VD: 15.000đ)</t>
+  </si>
+  <si>
+    <t>TC_SHIP_028</t>
+  </si>
+  <si>
+    <t>Shipping_Max_CharName</t>
+  </si>
+  <si>
+    <t>Nhập Tên vùng giao hàng dài (&gt; 255 ký tự)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập chuỗi 300 ký tự vào ô tên
+2. Bấm Lưu</t>
+  </si>
+  <si>
+    <t>Chuỗi 300 ký tự</t>
+  </si>
+  <si>
+    <t>Báo lỗi giới hạn ký tự hoặc tự cắt ngắn hợp lệ</t>
+  </si>
+  <si>
+    <t>TC_SHIP_029</t>
+  </si>
+  <si>
+    <t>Shipping_Responsive_Mobile</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị bảng trên thiết bị di động (375px)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Bật F12 Responsive 375px
+2. Xem bảng</t>
+  </si>
+  <si>
+    <t>Mobile View</t>
+  </si>
+  <si>
+    <t>Bảng có thanh cuộn ngang mượt mà, không vỡ layout giao diện</t>
+  </si>
+  <si>
+    <t>TC_SHIP_030</t>
+  </si>
+  <si>
+    <t>Shipping_API_GetSync</t>
+  </si>
+  <si>
+    <t>Đồng bộ dữ liệu bảng từ Backend API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. F5 tải lại trang
+2. Kiểm tra dữ liệu</t>
+  </si>
+  <si>
+    <t>GET /api/shipping-zones</t>
+  </si>
+  <si>
+    <t>Dữ liệu được tải động từ MySQL thông qua Laravel REST API</t>
+  </si>
+  <si>
+    <t>TC_SHIP_031</t>
+  </si>
+  <si>
+    <t>Shipping_XSS_Prevent</t>
+  </si>
+  <si>
+    <t>Kiểm tra chống mã độc XSS trong ô nhập tên vùng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập tên: "&lt;script&gt;alert(1)&lt;/script&gt;"
+2. Bấm Lưu</t>
+  </si>
+  <si>
+    <t>Payload XSS</t>
+  </si>
+  <si>
+    <t>Hệ thống escape ký tự an toàn, không thực thi mã script</t>
+  </si>
+  <si>
+    <t>TC_SHIP_032</t>
+  </si>
+  <si>
+    <t>Shipping_SQLi_Prevent</t>
+  </si>
+  <si>
+    <t>Kiểm tra chống SQL Injection trong ô tìm kiếm</t>
+  </si>
+  <si>
+    <t>1. Nhập: "' OR 1=1 --" vào ô tìm kiếm</t>
+  </si>
+  <si>
+    <t>Payload SQLi</t>
+  </si>
+  <si>
+    <t>Hệ thống xử lý an toàn qua Eloquent ORM, không lộ lỗi SQL</t>
   </si>
   <si>
     <t>Chức Năng Thanh Toán &amp; Tính Phí Ship</t>
@@ -460,14 +670,14 @@
     <t>Payment_UI</t>
   </si>
   <si>
-    <t>Kiểm tra giao diện trang Thanh Toán</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Thêm sản phẩm vào giỏ
-2. Vào trang /checkout</t>
-  </si>
-  <si>
-    <t>Hiển thị Form thông tin người nhận, chọn vùng giao hàng, 4 phương thức thanh toán, tóm tắt đơn hàng</t>
+    <t>Kiểm tra tải giao diện trang Thanh Toán</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Có hàng trong giỏ
+2. Vào /checkout</t>
+  </si>
+  <si>
+    <t>Hiển thị: Form thông tin nhận hàng, Vùng giao hàng, 4 Phương thức thanh toán, Tóm tắt giỏ hàng</t>
   </si>
   <si>
     <t>TC_PAY_002</t>
@@ -479,14 +689,14 @@
     <t>Truy cập checkout khi giỏ hàng trống</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Xóa hết giỏ hàng
-2. Vào /checkout</t>
-  </si>
-  <si>
-    <t>Giỏ hàng trống</t>
-  </si>
-  <si>
-    <t>Hiển thị thông báo "Giỏ hàng trống" kèm nút "Quay lại cửa hàng"</t>
+    <t xml:space="preserve">1. Giỏ hàng 0 sản phẩm
+2. Truy cập /checkout</t>
+  </si>
+  <si>
+    <t>Giỏ trống</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo "Giỏ hàng trống" kèm nút quay lại cửa hàng</t>
   </si>
   <si>
     <t>TC_PAY_003</t>
@@ -495,154 +705,334 @@
     <t>Payment_EmptySubmit</t>
   </si>
   <si>
-    <t>Nhấn Đặt hàng khi để trống toàn bộ thông tin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Để trống form
+    <t>Bấm Đặt hàng khi để trống toàn bộ Form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Không nhập gì
 2. Bấm "Đặt hàng ngay"</t>
   </si>
   <si>
-    <t>Form trống</t>
-  </si>
-  <si>
-    <t>Hiển thị thông báo lỗi dưới các trường bắt buộc (Họ tên, SĐT, Địa chỉ, Vùng giao hàng)</t>
+    <t>Form rỗng</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi đỏ dưới các trường bắt buộc (Họ tên, SĐT, Địa chỉ, Vùng giao hàng)</t>
   </si>
   <si>
     <t>TC_PAY_004</t>
   </si>
   <si>
-    <t>Payment_Phone_Invalid</t>
-  </si>
-  <si>
-    <t>Nhập Số điện thoại không đúng định dạng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Nhập SĐT chứa chữ cái hoặc không đủ 10 số
-2. Bấm Đặt hàng</t>
-  </si>
-  <si>
-    <t>SĐT: "09012abc" hoặc "123"</t>
+    <t>Payment_Name_Empty</t>
+  </si>
+  <si>
+    <t>Để trống trường Họ và tên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Điền đủ trường khác, bỏ trống Họ tên
+2. Đặt hàng</t>
+  </si>
+  <si>
+    <t>Họ tên: (Empty)</t>
+  </si>
+  <si>
+    <t>Báo lỗi "Vui lòng nhập họ tên"</t>
+  </si>
+  <si>
+    <t>TC_PAY_005</t>
+  </si>
+  <si>
+    <t>Payment_Phone_Empty</t>
+  </si>
+  <si>
+    <t>Để trống trường Số điện thoại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Bỏ trống SĐT
+2. Đặt hàng</t>
+  </si>
+  <si>
+    <t>SĐT: (Empty)</t>
+  </si>
+  <si>
+    <t>Báo lỗi "Vui lòng nhập số điện thoại"</t>
+  </si>
+  <si>
+    <t>TC_PAY_006</t>
+  </si>
+  <si>
+    <t>Payment_Phone_InvalidText</t>
+  </si>
+  <si>
+    <t>Nhập SĐT chứa chữ cái</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập SĐT: "0901abc123"
+2. Đặt hàng</t>
+  </si>
+  <si>
+    <t>SĐT: "0901abc123"</t>
   </si>
   <si>
     <t>Báo lỗi "Số điện thoại không hợp lệ"</t>
   </si>
   <si>
-    <t>TC_PAY_005</t>
-  </si>
-  <si>
-    <t>Payment_Phone_Valid</t>
-  </si>
-  <si>
-    <t>Nhập SĐT hợp lệ (đầu 0 hoặc +84)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Nhập SĐT 10 số chuẩn
-2. Bấm Đặt hàng</t>
-  </si>
-  <si>
-    <t>SĐT: "0901234567" hoặc "+84901234567"</t>
-  </si>
-  <si>
-    <t>Chấp nhận số điện thoại hợp lệ, không báo lỗi SĐT</t>
-  </si>
-  <si>
-    <t>TC_PAY_006</t>
+    <t>TC_PAY_007</t>
+  </si>
+  <si>
+    <t>Payment_Phone_InvalidLength</t>
+  </si>
+  <si>
+    <t>Nhập SĐT không đủ 10 số (VD: 5 số)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập SĐT: "09012"
+2. Đặt hàng</t>
+  </si>
+  <si>
+    <t>SĐT: "09012"</t>
+  </si>
+  <si>
+    <t>TC_PAY_008</t>
+  </si>
+  <si>
+    <t>Payment_Phone_Valid0x</t>
+  </si>
+  <si>
+    <t>Nhập SĐT 10 số đầu 0 hợp lệ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập SĐT chuẩn 10 số
+2. Đặt hàng</t>
+  </si>
+  <si>
+    <t>SĐT: "0909123456"</t>
+  </si>
+  <si>
+    <t>Hệ thống chấp nhận, không báo lỗi SĐT</t>
+  </si>
+  <si>
+    <t>TC_PAY_009</t>
+  </si>
+  <si>
+    <t>Payment_Phone_Valid84</t>
+  </si>
+  <si>
+    <t>Nhập SĐT chuẩn quốc tế (+84)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập SĐT: "+84909123456"
+2. Đặt hàng</t>
+  </si>
+  <si>
+    <t>SĐT: "+84909123456"</t>
+  </si>
+  <si>
+    <t>TC_PAY_010</t>
   </si>
   <si>
     <t>Payment_Email_Invalid</t>
   </si>
   <si>
-    <t>Nhập Email sai định dạng</t>
-  </si>
-  <si>
-    <t>1. Nhập email không có @ hoặc thiếu domain</t>
-  </si>
-  <si>
-    <t>Email: "nguyenvana@"</t>
+    <t>Nhập Email sai định dạng (thiếu @ hoặc domain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập Email: "nguyenvana"
+2. Đặt hàng</t>
+  </si>
+  <si>
+    <t>Email: "nguyenvana"</t>
   </si>
   <si>
     <t>Báo lỗi "Email không hợp lệ"</t>
   </si>
   <si>
-    <t>TC_PAY_007</t>
-  </si>
-  <si>
-    <t>Payment_Zone_Calc</t>
-  </si>
-  <si>
-    <t>Chọn Vùng giao hàng và kiểm tra tính phí ship</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Chọn vùng "Nội thành TP.HCM" (Phí 15.000đ, miễn phí từ 300.000đ)
-2. Kiểm tra phí ship</t>
-  </si>
-  <si>
-    <t>Đơn hàng: 150.000đ</t>
-  </si>
-  <si>
-    <t>Phí ship hiển thị 15.000đ, tổng tiền = Tạm tính + 15.000đ</t>
-  </si>
-  <si>
-    <t>TC_PAY_008</t>
-  </si>
-  <si>
-    <t>Payment_FreeShip</t>
-  </si>
-  <si>
-    <t>Kiểm tra Miễn phí vận chuyển khi đạt điều kiện</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Chọn vùng "Nội thành TP.HCM"
-2. Tổng tiền đơn &gt;= 300.000đ</t>
-  </si>
-  <si>
-    <t>Đơn hàng: 350.000đ</t>
-  </si>
-  <si>
-    <t>Phí ship hiển thị "Miễn phí 🎉", tổng tiền bằng đúng tiền hàng</t>
-  </si>
-  <si>
-    <t>TC_PAY_009</t>
+    <t>TC_PAY_011</t>
+  </si>
+  <si>
+    <t>Payment_Email_Valid</t>
+  </si>
+  <si>
+    <t>Nhập Email đúng định dạng chuẩn</t>
+  </si>
+  <si>
+    <t>1. Nhập Email chuẩn: "an.nguyen@gmail.com"</t>
+  </si>
+  <si>
+    <t>Email chuẩn</t>
+  </si>
+  <si>
+    <t>Chấp nhận email hợp lệ</t>
+  </si>
+  <si>
+    <t>TC_PAY_012</t>
+  </si>
+  <si>
+    <t>Payment_Address_Empty</t>
+  </si>
+  <si>
+    <t>Để trống Địa chỉ nhận hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Bỏ trống địa chỉ
+2. Đặt hàng</t>
+  </si>
+  <si>
+    <t>Địa chỉ: (Empty)</t>
+  </si>
+  <si>
+    <t>Báo lỗi "Vui lòng nhập địa chỉ"</t>
+  </si>
+  <si>
+    <t>TC_PAY_013</t>
+  </si>
+  <si>
+    <t>Payment_Zone_Empty</t>
+  </si>
+  <si>
+    <t>Chưa chọn Vùng giao hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Điền đủ thông tin nhưng chưa chọn vùng
+2. Đặt hàng</t>
+  </si>
+  <si>
+    <t>Vùng: Chưa chọn</t>
+  </si>
+  <si>
+    <t>Báo lỗi "Vui lòng chọn vùng giao hàng"</t>
+  </si>
+  <si>
+    <t>TC_PAY_014</t>
+  </si>
+  <si>
+    <t>Payment_Zone_InnerHCM</t>
+  </si>
+  <si>
+    <t>Tính phí ship vùng Nội thành TP.HCM (Đơn &lt; 300k)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Chọn vùng Nội thành TP.HCM (Phí 15.000đ)
+2. Tiền hàng = 150.000đ</t>
+  </si>
+  <si>
+    <t>Tổng hàng: 150.000đ</t>
+  </si>
+  <si>
+    <t>Phí ship hiển thị 15.000đ. Tổng cộng = 165.000đ</t>
+  </si>
+  <si>
+    <t>TC_PAY_015</t>
+  </si>
+  <si>
+    <t>Payment_Zone_OuterHCM</t>
+  </si>
+  <si>
+    <t>Tính phí ship vùng Ngoại thành TP.HCM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Chọn Ngoại thành TP.HCM (Phí 25.000đ)
+2. Tiền hàng = 200.000đ</t>
+  </si>
+  <si>
+    <t>Tổng hàng: 200.000đ</t>
+  </si>
+  <si>
+    <t>Phí ship hiển thị 25.000đ. Tổng cộng = 225.000đ</t>
+  </si>
+  <si>
+    <t>TC_PAY_016</t>
+  </si>
+  <si>
+    <t>Payment_Zone_North</t>
+  </si>
+  <si>
+    <t>Tính phí ship vùng Miền Bắc (Phí 50.000đ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Chọn Miền Bắc (Phí 50.000đ)
+2. Tiền hàng = 300.000đ</t>
+  </si>
+  <si>
+    <t>Tổng hàng: 300.000đ</t>
+  </si>
+  <si>
+    <t>Phí ship hiển thị 50.000đ. Tổng cộng = 350.000đ</t>
+  </si>
+  <si>
+    <t>TC_PAY_017</t>
+  </si>
+  <si>
+    <t>Payment_FreeShip_Reached</t>
+  </si>
+  <si>
+    <t>Kiểm tra Miễn phí ship khi đạt ngưỡng (Đơn &gt;= 300k)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Chọn Nội thành TP.HCM
+2. Tiền hàng = 350.000đ</t>
+  </si>
+  <si>
+    <t>Tổng hàng: 350.000đ</t>
+  </si>
+  <si>
+    <t>Phí ship đổi thành "Miễn phí 🎉". Tổng thanh toán bằng đúng tiền hàng (350.000đ)</t>
+  </si>
+  <si>
+    <t>TC_PAY_018</t>
+  </si>
+  <si>
+    <t>Payment_FreeShip_Notice</t>
+  </si>
+  <si>
+    <t>Hiển thị gợi ý số tiền cần mua thêm để freeship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Chọn Nội thành (Freeship từ 300k)
+2. Tiền hàng = 200.000đ</t>
+  </si>
+  <si>
+    <t>Thông báo hiển thị: "Mua thêm 100.000đ để được miễn phí ship"</t>
+  </si>
+  <si>
+    <t>TC_PAY_019</t>
   </si>
   <si>
     <t>Payment_Method_COD</t>
   </si>
   <si>
-    <t>Thanh toán bằng phương thức COD (Tiền mặt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Điền đủ form hợp lệ
-2. Chọn phương thức "COD"
+    <t>Thanh toán COD (Tiền mặt khi nhận)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Điền đủ form
+2. Chọn phương thức COD
 3. Bấm "Đặt hàng ngay"</t>
   </si>
   <si>
-    <t>Phương thức: COD</t>
-  </si>
-  <si>
-    <t>Xử lý 1.5s, chuyển đến màn hình "Đặt hàng thành công!" kèm Mã đơn hàng</t>
-  </si>
-  <si>
-    <t>TC_PAY_010</t>
+    <t>PT: COD</t>
+  </si>
+  <si>
+    <t>Tạo đơn qua API, chuyển sang màn hình thành công với mã đơn #GFxxxxxx</t>
+  </si>
+  <si>
+    <t>TC_PAY_020</t>
   </si>
   <si>
     <t>Payment_Method_Bank</t>
   </si>
   <si>
-    <t>Thanh toán Chuyển khoản Ngân hàng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Điền đủ form
-2. Chọn "Chuyển khoản ngân hàng"
-3. Bấm "Đặt hàng ngay"</t>
-  </si>
-  <si>
-    <t>Phương thức: Bank Transfer</t>
-  </si>
-  <si>
-    <t>Hiển thị popup thông tin tài khoản: Tên ngân hàng, Số TK, Chủ TK, Số tiền, Nội dung chuyển khoản và mã QR</t>
-  </si>
-  <si>
-    <t>TC_PAY_011</t>
+    <t>Thanh toán Chuyển khoản ngân hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Chọn "Chuyển khoản ngân hàng"
+2. Bấm "Đặt hàng ngay"</t>
+  </si>
+  <si>
+    <t>PT: Bank Transfer</t>
+  </si>
+  <si>
+    <t>Mở popup thông tin tài khoản: Số TK, Tên TK, Số tiền, Nội dung chuyển khoản và mã QR</t>
+  </si>
+  <si>
+    <t>TC_PAY_021</t>
   </si>
   <si>
     <t>Payment_Method_MoMo</t>
@@ -655,13 +1045,13 @@
 2. Bấm "Đặt hàng ngay"</t>
   </si>
   <si>
-    <t>Phương thức: MoMo</t>
-  </si>
-  <si>
-    <t>Hiển thị popup MoMo với mã QR thanh toán và số tiền cần chuyển</t>
-  </si>
-  <si>
-    <t>TC_PAY_012</t>
+    <t>PT: MoMo</t>
+  </si>
+  <si>
+    <t>Mở popup MoMo hiển thị mã QR và số tiền thanh toán</t>
+  </si>
+  <si>
+    <t>TC_PAY_022</t>
   </si>
   <si>
     <t>Payment_Method_VNPay</t>
@@ -674,58 +1064,148 @@
 2. Bấm "Đặt hàng ngay"</t>
   </si>
   <si>
-    <t>Phương thức: VNPay</t>
-  </si>
-  <si>
-    <t>Hiển thị popup cổng thanh toán VNPay</t>
-  </si>
-  <si>
-    <t>TC_PAY_013</t>
+    <t>PT: VNPay</t>
+  </si>
+  <si>
+    <t>Mở popup cổng VNPay hiển thị số tiền thanh toán</t>
+  </si>
+  <si>
+    <t>TC_PAY_023</t>
   </si>
   <si>
     <t>Payment_Popup_Confirm</t>
   </si>
   <si>
-    <t>Xác nhận thanh toán trên Popup Bank/MoMo/VNPay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Mở popup thanh toán
+    <t>Xác nhận thanh toán trên Popup trực tuyến</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Mở popup Bank/MoMo
 2. Bấm "Xác nhận đã thanh toán"</t>
   </si>
   <si>
-    <t>Đóng popup, chuyển sang màn hình "Đặt hàng thành công!", xóa giỏ hàng</t>
-  </si>
-  <si>
-    <t>TC_PAY_014</t>
+    <t>Đóng popup, tạo đơn thành công, giỏ hàng được xóa, hiển thị mã đơn hàng</t>
+  </si>
+  <si>
+    <t>TC_PAY_024</t>
   </si>
   <si>
     <t>Payment_Popup_Cancel</t>
   </si>
   <si>
-    <t>Hủy popup thanh toán trực tuyến</t>
+    <t>Hủy thanh toán trên Popup</t>
   </si>
   <si>
     <t xml:space="preserve">1. Mở popup Bank/MoMo
 2. Bấm "Hủy"</t>
   </si>
   <si>
-    <t>Đóng popup, giữ nguyên dữ liệu form và giỏ hàng</t>
-  </si>
-  <si>
-    <t>TC_PAY_015</t>
-  </si>
-  <si>
-    <t>Payment_Success_Link</t>
-  </si>
-  <si>
-    <t>Kiểm tra liên kết Theo dõi đơn trên màn hình Thành công</t>
+    <t>Popup đóng, form và giỏ hàng giữ nguyên vẹn</t>
+  </si>
+  <si>
+    <t>TC_PAY_025</t>
+  </si>
+  <si>
+    <t>Payment_Cart_Clear</t>
+  </si>
+  <si>
+    <t>Xóa giỏ hàng sau khi đặt hàng thành công</t>
   </si>
   <si>
     <t xml:space="preserve">1. Đặt hàng thành công
-2. Nhấn nút "Theo dõi đơn hàng"</t>
-  </si>
-  <si>
-    <t>Điều hướng đúng sang trang /tracking để kiểm tra lộ trình</t>
+2. Xem icon giỏ hàng trên navbar</t>
+  </si>
+  <si>
+    <t>Số lượng badge giỏ hàng trở về 0, giỏ hàng trống</t>
+  </si>
+  <si>
+    <t>TC_PAY_026</t>
+  </si>
+  <si>
+    <t>Payment_Tracking_Redirect</t>
+  </si>
+  <si>
+    <t>Nhấn nút "Theo dõi đơn hàng" trên màn hình Thành công</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Đặt hàng thành công
+2. Bấm nút "Theo dõi đơn hàng"</t>
+  </si>
+  <si>
+    <t>Điều hướng chuẩn sang trang /tracking</t>
+  </si>
+  <si>
+    <t>TC_PAY_027</t>
+  </si>
+  <si>
+    <t>Payment_Order_DBSync</t>
+  </si>
+  <si>
+    <t>Kiểm tra lưu đơn hàng vào CSDL MySQL Backend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Hoàn tất đặt đơn
+2. Tra cứu mã đơn trong DB</t>
+  </si>
+  <si>
+    <t>Mã đơn sinh ra</t>
+  </si>
+  <si>
+    <t>Đơn hàng và các item tương ứng được lưu chuẩn xác vào bảng `orders` &amp; `order_items`</t>
+  </si>
+  <si>
+    <t>TC_PAY_028</t>
+  </si>
+  <si>
+    <t>Payment_Switch_Zone</t>
+  </si>
+  <si>
+    <t>Đổi vùng giao hàng nhiều lần trong lúc điền form</t>
+  </si>
+  <si>
+    <t>1. Chọn vùng A rồi đổi sang vùng B</t>
+  </si>
+  <si>
+    <t>Nội thành -&gt; Miền Bắc</t>
+  </si>
+  <si>
+    <t>Phí ship và Tổng cộng tự động cập nhật lại tương ứng</t>
+  </si>
+  <si>
+    <t>TC_PAY_029</t>
+  </si>
+  <si>
+    <t>Payment_Notes_SpecialChars</t>
+  </si>
+  <si>
+    <t>Nhập Ghi chú đơn hàng có dấu và emoji</t>
+  </si>
+  <si>
+    <t>1. Nhập: "Giao giờ hành chính giúp em ạ 🌿📦"</t>
+  </si>
+  <si>
+    <t>Ghi chú tiếng Việt</t>
+  </si>
+  <si>
+    <t>Lưu chuẩn xác chuỗi UTF-8 vào CSDL</t>
+  </si>
+  <si>
+    <t>TC_PAY_030</t>
+  </si>
+  <si>
+    <t>Payment_Responsive</t>
+  </si>
+  <si>
+    <t>Kiểm tra giao diện Thanh toán trên iPad / Tablet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Bật F12 Responsive 768px
+2. Quan sát 2 cột</t>
+  </si>
+  <si>
+    <t>Tablet View</t>
+  </si>
+  <si>
+    <t>Cột form và Cột tóm tắt bố cục hợp lý, dễ thao tác</t>
   </si>
   <si>
     <t>Tích Hợp Bản Đồ Nhà Vườn (GIS)</t>
@@ -737,73 +1217,169 @@
     <t>TC_MAP_001</t>
   </si>
   <si>
-    <t>Map_UI</t>
-  </si>
-  <si>
-    <t>Kiểm tra tải giao diện Bản đồ Nhà Vườn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Truy cập trang /map
+    <t>Map_Load</t>
+  </si>
+  <si>
+    <t>Kiểm tra tải giao diện Bản đồ GIS Nhà Vườn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Truy cập /map
 2. Quan sát</t>
   </si>
   <si>
-    <t>Hiển thị bản đồ Leaflet OpenStreetMap toàn cảnh Việt Nam, danh sách nông hộ bên trái, ô tìm kiếm và các nút lọc vùng</t>
+    <t>Hiển thị Bản đồ Leaflet OpenStreetMap, Sidebar danh sách nhà vườn, Ô tìm kiếm và Bộ lọc vùng</t>
   </si>
   <si>
     <t>TC_MAP_002</t>
   </si>
   <si>
-    <t>Map_Markers</t>
-  </si>
-  <si>
-    <t>Hiển thị các ghim vị trí (Markers) nhà vườn trên bản đồ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Mở trang /map
-2. Quan sát các điểm ghim</t>
-  </si>
-  <si>
-    <t>Các điểm ghim xuất hiện đúng tọa độ địa lý các tỉnh (Bến Tre, Vĩnh Long, Đà Lạt, Đồng Tháp, Mộc Châu, Thái Nguyên...)</t>
+    <t>Map_Tiles_Render</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị bản đồ nền OpenStreetMap</t>
+  </si>
+  <si>
+    <t>1. Xem khu vực bản đồ</t>
+  </si>
+  <si>
+    <t>Bản đồ nền load đầy đủ các mảnh tile, không bị xám hoặc đứt gãy</t>
   </si>
   <si>
     <t>TC_MAP_003</t>
   </si>
   <si>
-    <t>Map_Marker_Popup</t>
-  </si>
-  <si>
-    <t>Nhấn vào Marker trên bản đồ để xem tóm tắt</t>
-  </si>
-  <si>
-    <t>1. Click vào 1 marker bất kỳ trên bản đồ</t>
-  </si>
-  <si>
-    <t>Marker nhà vườn</t>
-  </si>
-  <si>
-    <t>Popup mở ra hiển thị: Ảnh nông trại, Tên nhà vườn, Địa chỉ, Đánh giá sao, Số sản phẩm và Đặc sản</t>
+    <t>Map_Center_Vietnam</t>
+  </si>
+  <si>
+    <t>Kiểm tra tọa độ trung tâm khởi tạo</t>
+  </si>
+  <si>
+    <t>1. Tải trang /map</t>
+  </si>
+  <si>
+    <t>Bản đồ lấy trung tâm toàn cảnh Việt Nam (Khoảng [14.0583, 108.2772]) ở mức zoom 6</t>
   </si>
   <si>
     <t>TC_MAP_004</t>
   </si>
   <si>
+    <t>Map_Zoom_Controls</t>
+  </si>
+  <si>
+    <t>Kiểm tra nút Phóng to / Thu nhỏ (+ / -)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click nút + và - trên bản đồ
+2. Lăn chuột cuộn zoom</t>
+  </si>
+  <si>
+    <t>Zoom action</t>
+  </si>
+  <si>
+    <t>Bản đồ phóng to / thu nhỏ mượt mà</t>
+  </si>
+  <si>
+    <t>TC_MAP_005</t>
+  </si>
+  <si>
+    <t>Map_Pan_Drag</t>
+  </si>
+  <si>
+    <t>Kiểm tra kéo rê bản đồ (Pan/Drag)</t>
+  </si>
+  <si>
+    <t>1. Giữ chuột kéo bản đồ sang trái/phải</t>
+  </si>
+  <si>
+    <t>Drag action</t>
+  </si>
+  <si>
+    <t>Bản đồ di chuyển theo vị trí chuột trơn tru</t>
+  </si>
+  <si>
+    <t>TC_MAP_006</t>
+  </si>
+  <si>
+    <t>Map_Markers_Display</t>
+  </si>
+  <si>
+    <t>Hiển thị các Marker nhà vườn trên bản đồ</t>
+  </si>
+  <si>
+    <t>1. Quan sát các điểm ghim</t>
+  </si>
+  <si>
+    <t>Các điểm ghim xuất hiện đúng tọa độ địa lý các tỉnh (Bến Tre, Vĩnh Long, Đà Lạt, Mộc Châu, Thái Nguyên...)</t>
+  </si>
+  <si>
+    <t>TC_MAP_007</t>
+  </si>
+  <si>
+    <t>Map_Marker_ClickPopup</t>
+  </si>
+  <si>
+    <t>Nhấn vào Marker để mở Popup tóm tắt</t>
+  </si>
+  <si>
+    <t>1. Click vào 1 Marker trên map</t>
+  </si>
+  <si>
+    <t>Marker bất kỳ</t>
+  </si>
+  <si>
+    <t>Popup mở ra hiển thị: Ảnh nông trại, Tên nhà vườn, Địa chỉ, Số sao ⭐, Số sản phẩm và Đặc sản</t>
+  </si>
+  <si>
+    <t>TC_MAP_008</t>
+  </si>
+  <si>
+    <t>Map_Popup_Close</t>
+  </si>
+  <si>
+    <t>Đóng Popup khi click ra vùng ngoài bản đồ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Mở popup của 1 marker
+2. Click vào vị trí trống trên map</t>
+  </si>
+  <si>
+    <t>Popup đóng lại</t>
+  </si>
+  <si>
+    <t>TC_MAP_009</t>
+  </si>
+  <si>
     <t>Map_Search_Name</t>
   </si>
   <si>
-    <t>Tìm kiếm nhà vườn theo Tên hoặc Địa chỉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Nhập "Đà Lạt" vào ô tìm kiếm
-2. Quan sát danh sách và map</t>
+    <t>Tìm kiếm nhà vườn theo Tên nhà vườn</t>
+  </si>
+  <si>
+    <t>1. Nhập "Đà Lạt" vào ô tìm kiếm</t>
   </si>
   <si>
     <t>Từ khóa: "Đà Lạt"</t>
   </si>
   <si>
-    <t>Danh sách lọc ra các nhà vườn tại Đà Lạt, hiển thị số lượng kết quả tìm thấy</t>
-  </si>
-  <si>
-    <t>TC_MAP_005</t>
+    <t>Sidebar và Bản đồ chỉ hiển thị các nông hộ có tên chứa "Đà Lạt"</t>
+  </si>
+  <si>
+    <t>TC_MAP_010</t>
+  </si>
+  <si>
+    <t>Map_Search_Province</t>
+  </si>
+  <si>
+    <t>Tìm kiếm nhà vườn theo Tỉnh thành</t>
+  </si>
+  <si>
+    <t>1. Nhập "Bến Tre" vào ô tìm kiếm</t>
+  </si>
+  <si>
+    <t>Hiển thị đúng nông hộ Vườn Chú Ba tại Bến Tre</t>
+  </si>
+  <si>
+    <t>TC_MAP_011</t>
   </si>
   <si>
     <t>Map_Search_Specialty</t>
@@ -818,25 +1394,28 @@
     <t>Từ khóa: "sầu riêng"</t>
   </si>
   <si>
-    <t>Hiển thị các nông hộ chuyên canh Sầu riêng (như Vườn Chú Ba - Bến Tre)</t>
-  </si>
-  <si>
-    <t>TC_MAP_006</t>
-  </si>
-  <si>
-    <t>Map_Search_Empty</t>
+    <t>Hiển thị các nông hộ chuyên canh sầu riêng</t>
+  </si>
+  <si>
+    <t>TC_MAP_012</t>
+  </si>
+  <si>
+    <t>Map_Search_NoResult</t>
   </si>
   <si>
     <t>Tìm kiếm với từ khóa không khớp</t>
   </si>
   <si>
+    <t>1. Nhập "HaNoi12345"</t>
+  </si>
+  <si>
     <t>Từ khóa: "HaNoi12345"</t>
   </si>
   <si>
-    <t>Hiển thị thông báo "Không tìm thấy nhà vườn nào"</t>
-  </si>
-  <si>
-    <t>TC_MAP_007</t>
+    <t>Sidebar hiển thị thông báo "Không tìm thấy nhà vườn nào"</t>
+  </si>
+  <si>
+    <t>TC_MAP_013</t>
   </si>
   <si>
     <t>Map_Filter_North</t>
@@ -848,13 +1427,13 @@
     <t>1. Nhấn nút lọc "Miền Bắc"</t>
   </si>
   <si>
-    <t>Filter: North</t>
-  </si>
-  <si>
-    <t>Chỉ hiển thị các nông hộ Miền Bắc (Trang Trại Mộc Châu, HTX Chè Thái Nguyên)</t>
-  </si>
-  <si>
-    <t>TC_MAP_008</t>
+    <t>Zone: North</t>
+  </si>
+  <si>
+    <t>Chỉ hiển thị các nông hộ Miền Bắc (Mộc Châu, Thái Nguyên), nút "Miền Bắc" active màu xanh</t>
+  </si>
+  <si>
+    <t>TC_MAP_014</t>
   </si>
   <si>
     <t>Map_Filter_Central</t>
@@ -866,13 +1445,13 @@
     <t>1. Nhấn nút lọc "Miền Trung"</t>
   </si>
   <si>
-    <t>Filter: Central</t>
-  </si>
-  <si>
-    <t>Chỉ hiển thị các nông hộ Miền Trung (Nông Trại Xanh Đà Lạt, Rau Hữu Cơ Đà Nẵng)</t>
-  </si>
-  <si>
-    <t>TC_MAP_009</t>
+    <t>Zone: Central</t>
+  </si>
+  <si>
+    <t>Chỉ hiển thị nông hộ Miền Trung (Đà Lạt, Lâm Đồng)</t>
+  </si>
+  <si>
+    <t>TC_MAP_015</t>
   </si>
   <si>
     <t>Map_Filter_South</t>
@@ -884,13 +1463,13 @@
     <t>1. Nhấn nút lọc "Miền Nam"</t>
   </si>
   <si>
-    <t>Filter: South</t>
-  </si>
-  <si>
-    <t>Chỉ hiển thị các nông hộ Miền Nam (Bến Tre, Vĩnh Long, Đồng Tháp)</t>
-  </si>
-  <si>
-    <t>TC_MAP_010</t>
+    <t>Zone: South</t>
+  </si>
+  <si>
+    <t>Chỉ hiển thị nông hộ Miền Nam (Bến Tre, Vĩnh Long, Đồng Tháp)</t>
+  </si>
+  <si>
+    <t>TC_MAP_016</t>
   </si>
   <si>
     <t>Map_Filter_All</t>
@@ -903,44 +1482,211 @@
 2. Nhấn "Tất cả vùng"</t>
   </si>
   <si>
-    <t>Filter: All</t>
-  </si>
-  <si>
-    <t>Hiển thị lại toàn bộ các nhà vườn trên toàn quốc</t>
-  </si>
-  <si>
-    <t>TC_MAP_011</t>
-  </si>
-  <si>
-    <t>Map_Farm_Detail</t>
-  </si>
-  <si>
-    <t>Nhấn vào Card nhà vườn để mở Modal chi tiết</t>
-  </si>
-  <si>
-    <t>1. Nhấn vào 1 nhà vườn trong danh sách</t>
-  </si>
-  <si>
-    <t>Vườn Trái Cây Chú Ba</t>
-  </si>
-  <si>
-    <t>Modal chi tiết hiển thị: Banner lớn, Tên vườn, Chủ vườn, Địa chỉ, Đánh giá, Huy hiệu VietGAP, Đặc sản, Tọa độ GPS, Nút "Xem sản phẩm"</t>
-  </si>
-  <si>
-    <t>TC_MAP_012</t>
-  </si>
-  <si>
-    <t>Map_Detail_Close</t>
-  </si>
-  <si>
-    <t>Đóng Modal chi tiết nhà vườn</t>
+    <t>Zone: All</t>
+  </si>
+  <si>
+    <t>Hiển thị lại toàn bộ các nhà vườn trên cả nước</t>
+  </si>
+  <si>
+    <t>TC_MAP_017</t>
+  </si>
+  <si>
+    <t>Map_Combine_SearchFilter</t>
+  </si>
+  <si>
+    <t>Kết hợp Tìm kiếm từ khóa và Lọc vùng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Chọn lọc "Miền Nam"
+2. Nhập từ khóa: "Bưởi"</t>
+  </si>
+  <si>
+    <t>Zone: South, Key: "Bưởi"</t>
+  </si>
+  <si>
+    <t>Hiển thị HTX Bưởi Da Xanh tại Vĩnh Long</t>
+  </si>
+  <si>
+    <t>TC_MAP_018</t>
+  </si>
+  <si>
+    <t>Map_Sidebar_ListClick</t>
+  </si>
+  <si>
+    <t>Nhấn vào Card nhà vườn trong Sidebar</t>
+  </si>
+  <si>
+    <t>1. Click vào Card "Vườn Trái Cây Chú Ba"</t>
+  </si>
+  <si>
+    <t>Card chú Ba</t>
+  </si>
+  <si>
+    <t>Mở Modal chi tiết đầy đủ thông tin của nhà vườn</t>
+  </si>
+  <si>
+    <t>TC_MAP_019</t>
+  </si>
+  <si>
+    <t>Map_VietGAP_Badge</t>
+  </si>
+  <si>
+    <t>Hiển thị huy hiệu VietGAP cho nhà vườn đạt chuẩn</t>
+  </si>
+  <si>
+    <t>1. Xem các nhà vườn có is_verified = true</t>
+  </si>
+  <si>
+    <t>Badge xanh "VietGAP" hiển thị nổi bật trên card và modal</t>
+  </si>
+  <si>
+    <t>TC_MAP_020</t>
+  </si>
+  <si>
+    <t>Map_Detail_ModalInfo</t>
+  </si>
+  <si>
+    <t>Kiểm tra thông tin trên Modal chi tiết nhà vườn</t>
+  </si>
+  <si>
+    <t>1. Mở modal chi tiết</t>
+  </si>
+  <si>
+    <t>Hiển thị: Ảnh bìa lớn, Tên vườn, Tên chủ vườn, Địa chỉ, Đánh giá, Đặc sản, Tọa độ GPS, Nút "Xem sản phẩm"</t>
+  </si>
+  <si>
+    <t>TC_MAP_021</t>
+  </si>
+  <si>
+    <t>Map_Detail_GPSFormat</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị Tọa độ GPS trên Modal</t>
   </si>
   <si>
     <t xml:space="preserve">1. Mở modal chi tiết
-2. Nhấn nút X hoặc click ra ngoài</t>
-  </si>
-  <si>
-    <t>Modal đóng mượt mà, trở lại giao diện bản đồ</t>
+2. Xem dòng Tọa độ GPS</t>
+  </si>
+  <si>
+    <t>Tọa độ hiển thị đúng chuẩn số thập phân (VD: 10.2348, 106.3485)</t>
+  </si>
+  <si>
+    <t>TC_MAP_022</t>
+  </si>
+  <si>
+    <t>Map_Detail_ProductsLink</t>
+  </si>
+  <si>
+    <t>Nhấn nút "Xem sản phẩm" trên Modal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Mở modal
+2. Nhấn nút "Xem sản phẩm"</t>
+  </si>
+  <si>
+    <t>Điều hướng người dùng đến trang danh mục sản phẩm</t>
+  </si>
+  <si>
+    <t>TC_MAP_023</t>
+  </si>
+  <si>
+    <t>Map_Detail_CloseBtn</t>
+  </si>
+  <si>
+    <t>Đóng Modal bằng nút X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Mở modal
+2. Click nút X góc trên</t>
+  </si>
+  <si>
+    <t>Modal đóng lại mượt mà</t>
+  </si>
+  <si>
+    <t>TC_MAP_024</t>
+  </si>
+  <si>
+    <t>Map_Detail_CloseBackdrop</t>
+  </si>
+  <si>
+    <t>Đóng Modal bằng cách click vùng tối bên ngoài</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Mở modal
+2. Click ra ngoài backdrop đen</t>
+  </si>
+  <si>
+    <t>Modal đóng lại</t>
+  </si>
+  <si>
+    <t>TC_MAP_025</t>
+  </si>
+  <si>
+    <t>Map_API_Sync</t>
+  </si>
+  <si>
+    <t>Đồng bộ dữ liệu nông hộ từ Backend API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Tải trang /map
+2. Kiểm tra network</t>
+  </si>
+  <si>
+    <t>GET /api/farmers</t>
+  </si>
+  <si>
+    <t>Tọa độ và dữ liệu nông hộ được fetch trực tiếp từ Laravel CSDL MySQL</t>
+  </si>
+  <si>
+    <t>TC_MAP_026</t>
+  </si>
+  <si>
+    <t>Map_Responsive_Layout</t>
+  </si>
+  <si>
+    <t>Kiểm tra responsive trên Mobile (&lt; 1024px)</t>
+  </si>
+  <si>
+    <t>1. Chuyển sang kích thước điện thoại</t>
+  </si>
+  <si>
+    <t>Bản đồ hiển thị phía trên, danh sách nông hộ trượt xuống phía dưới</t>
+  </si>
+  <si>
+    <t>TC_MAP_027</t>
+  </si>
+  <si>
+    <t>Map_Star_RatingDisplay</t>
+  </si>
+  <si>
+    <t>Hiển thị số sao đánh giá trung bình</t>
+  </si>
+  <si>
+    <t>1. Xem điểm rating của nông hộ</t>
+  </si>
+  <si>
+    <t>Rating: 4.8</t>
+  </si>
+  <si>
+    <t>Hiển thị icon ngôi sao vàng kèm điểm số chính xác</t>
+  </si>
+  <si>
+    <t>TC_MAP_028</t>
+  </si>
+  <si>
+    <t>Map_Specialty_Badge</t>
+  </si>
+  <si>
+    <t>Hiển thị tag vùng miền đúng màu</t>
+  </si>
+  <si>
+    <t>1. Xem tag vùng miền trên từng card</t>
+  </si>
+  <si>
+    <t>Zone tags</t>
+  </si>
+  <si>
+    <t>Miền Bắc (Xanh dương), Miền Trung (Cam), Miền Nam (Xanh lá)</t>
   </si>
   <si>
     <t>Chức Năng Theo Dõi Hành Trình Đơn Hàng</t>
@@ -955,20 +1701,20 @@
     <t>Track_UI</t>
   </si>
   <si>
-    <t>Kiểm tra giao diện trang Theo Dõi Đơn Hàng</t>
+    <t>Kiểm tra tải giao diện trang Theo Dõi Đơn Hàng</t>
   </si>
   <si>
     <t xml:space="preserve">1. Truy cập /tracking
 2. Quan sát</t>
   </si>
   <si>
-    <t>Hiển thị Banner Hero xanh, ô nhập mã đơn hàng, nút Tra cứu và các mã đơn mẫu gợi ý</t>
+    <t>Hiển thị Banner gradient xanh, Ô nhập mã đơn, Nút Tra cứu, Dãy nút chip gợi ý mã mẫu</t>
   </si>
   <si>
     <t>TC_TRACK_002</t>
   </si>
   <si>
-    <t>Track_Empty</t>
+    <t>Track_EmptyCode</t>
   </si>
   <si>
     <t>Nhấn Tra cứu khi để trống ô mã đơn</t>
@@ -978,154 +1724,774 @@
 2. Nhấn "Tra cứu"</t>
   </si>
   <si>
-    <t>Mã đơn: (Empty)</t>
-  </si>
-  <si>
-    <t>Báo lỗi "Vui lòng nhập mã đơn hàng"</t>
+    <t>Mã: (Empty)</t>
+  </si>
+  <si>
+    <t>Không gọi API, ô input giữ focus hoặc hiển thị thông báo</t>
   </si>
   <si>
     <t>TC_TRACK_003</t>
   </si>
   <si>
+    <t>Track_EnterKey</t>
+  </si>
+  <si>
+    <t>Nhấn phím Enter để thực hiện tra cứu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập "GF284910"
+2. Nhấn Enter trên bàn phím</t>
+  </si>
+  <si>
+    <t>Mã: "GF284910"</t>
+  </si>
+  <si>
+    <t>Kích hoạt tìm kiếm và hiển thị kết quả đúng như bấm nút Tra cứu</t>
+  </si>
+  <si>
+    <t>TC_TRACK_004</t>
+  </si>
+  <si>
     <t>Track_NotFound</t>
   </si>
   <si>
-    <t>Tra cứu mã đơn hàng không tồn tại</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Nhập mã đơn sai
-2. Nhấn "Tra cứu"</t>
+    <t>Tra cứu với mã đơn hàng không tồn tại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập mã sai: "GF999999"
+2. Bấm Tra cứu</t>
   </si>
   <si>
     <t>Mã: "GF999999"</t>
   </si>
   <si>
-    <t>Báo lỗi không tìm thấy đơn hàng, kèm gợi ý các mã mẫu có sẵn</t>
-  </si>
-  <si>
-    <t>TC_TRACK_004</t>
-  </si>
-  <si>
-    <t>Track_Shipping_Order</t>
-  </si>
-  <si>
-    <t>Tra cứu đơn hàng đang trong trạng thái "Đang giao"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Nhập mã đơn đang giao
-2. Nhấn "Tra cứu"</t>
-  </si>
-  <si>
-    <t>Mã: "GF284910"</t>
-  </si>
-  <si>
-    <t>Hiển thị Timeline: Bước 1 (Đặt hàng - Xong), Bước 2 (Xác nhận - Xong), Bước 3 (Đang giao - Hoạt ảnh pulse xanh), Bước 4 (Chờ giao)</t>
+    <t>Hiển thị thông báo đỏ "Không tìm thấy đơn hàng #GF999999" kèm gợi ý mã mẫu</t>
   </si>
   <si>
     <t>TC_TRACK_005</t>
   </si>
   <si>
-    <t>Track_Shipping_Map</t>
-  </si>
-  <si>
-    <t>Hiển thị Bản đồ vị trí Shipper khi đang giao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Tra cứu đơn "GF284910" (đang giao)
-2. Quan sát khu vực bản đồ</t>
-  </si>
-  <si>
-    <t>Hiển thị Bản đồ mini tương tác có 2 điểm: Vị trí Shipper (icon xe máy) và Điểm giao hàng của khách</t>
+    <t>Track_Pill_Click</t>
+  </si>
+  <si>
+    <t>Nhấn vào nút chip mã mẫu gợi ý</t>
+  </si>
+  <si>
+    <t>1. Click vào pill "GF284910"</t>
+  </si>
+  <si>
+    <t>Pill "GF284910"</t>
+  </si>
+  <si>
+    <t>Mã tự động điền vào ô tìm kiếm và kích hoạt tra cứu ngay lập tức</t>
   </si>
   <si>
     <t>TC_TRACK_006</t>
   </si>
   <si>
+    <t>Track_Case_Insensitive</t>
+  </si>
+  <si>
+    <t>Tra cứu mã đơn bằng chữ thường (gf284910)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập "gf284910"
+2. Bấm Tra cứu</t>
+  </si>
+  <si>
+    <t>Mã: "gf284910"</t>
+  </si>
+  <si>
+    <t>Hệ thống tự viết hoa thành GF284910 và trả về kết quả đúng</t>
+  </si>
+  <si>
+    <t>TC_TRACK_007</t>
+  </si>
+  <si>
+    <t>Track_Hash_Prefix</t>
+  </si>
+  <si>
+    <t>Tra cứu mã đơn có dấu thăng (#GF284910)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập "#GF284910"
+2. Bấm Tra cứu</t>
+  </si>
+  <si>
+    <t>Mã: "#GF284910"</t>
+  </si>
+  <si>
+    <t>Hệ thống tự bỏ dấu # và tra cứu chính xác đơn GF284910</t>
+  </si>
+  <si>
+    <t>TC_TRACK_008</t>
+  </si>
+  <si>
+    <t>Track_Status_Pending</t>
+  </si>
+  <si>
+    <t>Tra cứu đơn hàng trạng thái "Chờ xác nhận"</t>
+  </si>
+  <si>
+    <t>1. Tra cứu đơn mới tạo</t>
+  </si>
+  <si>
+    <t>Status: Pending</t>
+  </si>
+  <si>
+    <t>Badge "Chờ xác nhận" (màu vàng). Bước 1 "Đặt hàng" hoàn thành</t>
+  </si>
+  <si>
+    <t>TC_TRACK_009</t>
+  </si>
+  <si>
+    <t>Track_Status_Confirmed</t>
+  </si>
+  <si>
+    <t>Tra cứu đơn hàng trạng thái "Đã xác nhận"</t>
+  </si>
+  <si>
+    <t>1. Tra cứu mã "GF285130"</t>
+  </si>
+  <si>
+    <t>Mã: "GF285130"</t>
+  </si>
+  <si>
+    <t>Badge "Đã xác nhận" (màu xanh dương). Bước 1 và Bước 2 hoàn thành</t>
+  </si>
+  <si>
+    <t>TC_TRACK_010</t>
+  </si>
+  <si>
+    <t>Track_Status_Shipping</t>
+  </si>
+  <si>
+    <t>Tra cứu đơn hàng trạng thái "Đang giao hàng"</t>
+  </si>
+  <si>
+    <t>1. Tra cứu mã "GF284910"</t>
+  </si>
+  <si>
+    <t>Badge "Đang giao hàng" (màu tím). Bước 3 "Đang giao" có hiệu ứng pulse nhấp nháy</t>
+  </si>
+  <si>
+    <t>TC_TRACK_011</t>
+  </si>
+  <si>
+    <t>Track_Status_Delivered</t>
+  </si>
+  <si>
+    <t>Tra cứu đơn hàng trạng thái "Đã giao thành công"</t>
+  </si>
+  <si>
+    <t>1. Tra cứu mã "GF285020"</t>
+  </si>
+  <si>
+    <t>Mã: "GF285020"</t>
+  </si>
+  <si>
+    <t>Badge "Đã giao thành công" (màu xanh lá). Cả 4 bước Timeline đều có dấu tick xanh</t>
+  </si>
+  <si>
+    <t>TC_TRACK_012</t>
+  </si>
+  <si>
+    <t>Track_Timeline_Timestamps</t>
+  </si>
+  <si>
+    <t>Kiểm tra mốc thời gian hiển thị trên từng bước Timeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Tra cứu đơn "GF285020"
+2. Xem các mốc giờ</t>
+  </si>
+  <si>
+    <t>Mỗi bước đã hoàn thành có mốc ngày giờ cụ thể (VD: 18/08 14:00)</t>
+  </si>
+  <si>
+    <t>TC_TRACK_013</t>
+  </si>
+  <si>
+    <t>Track_Shipper_MapDisplay</t>
+  </si>
+  <si>
+    <t>Hiển thị Bản đồ mini khi đơn hàng đang giao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Tra cứu đơn "GF284910" (Shipping)
+2. Quan sát khu vực Map</t>
+  </si>
+  <si>
+    <t>Bản đồ Leaflet hiển thị với 2 Marker: Vị trí Shipper (🛵) và Điểm nhận hàng (📍)</t>
+  </si>
+  <si>
+    <t>TC_TRACK_014</t>
+  </si>
+  <si>
+    <t>Track_Shipper_MapHide</t>
+  </si>
+  <si>
+    <t>Ẩn Bản đồ khi đơn hàng đã giao thành công</t>
+  </si>
+  <si>
+    <t>1. Tra cứu đơn "GF285020" (Delivered)</t>
+  </si>
+  <si>
+    <t>Không hiển thị bản đồ shipper vì đơn hàng đã kết thúc</t>
+  </si>
+  <si>
+    <t>TC_TRACK_015</t>
+  </si>
+  <si>
     <t>Track_Shipper_Info</t>
   </si>
   <si>
-    <t>Hiển thị thông tin Shipper phụ trách đơn</t>
+    <t>Hiển thị thông tin Shipper phụ trách</t>
   </si>
   <si>
     <t xml:space="preserve">1. Tra cứu đơn "GF284910"
-2. Xem mục Thông tin shipper</t>
-  </si>
-  <si>
-    <t>Hiển thị đúng Tên shipper ("Trần Minh Đức") và Số điện thoại liên hệ ("0912345678")</t>
-  </si>
-  <si>
-    <t>TC_TRACK_007</t>
-  </si>
-  <si>
-    <t>Track_Delivered_Order</t>
-  </si>
-  <si>
-    <t>Tra cứu đơn hàng đã giao thành công</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Nhập mã đơn hoàn thành
-2. Nhấn "Tra cứu"</t>
-  </si>
-  <si>
-    <t>Mã: "GF285020"</t>
-  </si>
-  <si>
-    <t>Badge trạng thái "Đã giao thành công", cả 4 bước Timeline đều hiển thị dấu tick xanh kèm thời gian cụ thể</t>
-  </si>
-  <si>
-    <t>TC_TRACK_008</t>
-  </si>
-  <si>
-    <t>Track_Confirmed_Order</t>
-  </si>
-  <si>
-    <t>Tra cứu đơn hàng vừa xác nhận</t>
-  </si>
-  <si>
-    <t>1. Nhập mã đơn mới xác nhận</t>
-  </si>
-  <si>
-    <t>Mã: "GF285130"</t>
-  </si>
-  <si>
-    <t>Bước "Xác nhận" đang xử lý, bước "Đang giao" và "Đã giao" hiển thị chờ</t>
-  </si>
-  <si>
-    <t>TC_TRACK_009</t>
-  </si>
-  <si>
-    <t>Track_Order_Detail</t>
-  </si>
-  <si>
-    <t>Hiển thị chi tiết sản phẩm và tổng tiền đơn hàng</t>
+2. Xem card Shipper</t>
+  </si>
+  <si>
+    <t>Hiển thị đúng Tên shipper ("Trần Minh Đức") và Số điện thoại ("0912345678")</t>
+  </si>
+  <si>
+    <t>TC_TRACK_016</t>
+  </si>
+  <si>
+    <t>Track_Shipper_CallBtn</t>
+  </si>
+  <si>
+    <t>Kiểm tra nút Gọi điện cho Shipper</t>
+  </si>
+  <si>
+    <t>1. Bấm nút "Gọi điện" trên card shipper</t>
+  </si>
+  <si>
+    <t>Trình duyệt kích hoạt giao thức tel: mở ứng dụng gọi điện với SĐT shipper</t>
+  </si>
+  <si>
+    <t>TC_TRACK_017</t>
+  </si>
+  <si>
+    <t>Track_Customer_Info</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị Thông tin người nhận</t>
   </si>
   <si>
     <t xml:space="preserve">1. Tra cứu đơn bất kỳ
-2. Quan sát danh sách sản phẩm</t>
-  </si>
-  <si>
-    <t>Mã đơn hợp lệ</t>
-  </si>
-  <si>
-    <t>Hiển thị đầy đủ: Tên sản phẩm, đơn vị, số lượng, đơn giá, tạm tính, phí giao hàng và tổng thanh toán chính xác</t>
-  </si>
-  <si>
-    <t>TC_TRACK_010</t>
-  </si>
-  <si>
-    <t>Track_Quick_Pill</t>
-  </si>
-  <si>
-    <t>Nhấn vào nút chip mã đơn gợi ý</t>
-  </si>
-  <si>
-    <t>1. Click vào mã "GF284910" ở hàng gợi ý</t>
-  </si>
-  <si>
-    <t>Click pill "GF284910"</t>
-  </si>
-  <si>
-    <t>Mã tự động điền vào ô tìm kiếm nhanh chóng</t>
+2. Xem card Thông tin nhận hàng</t>
+  </si>
+  <si>
+    <t>Mã hợp lệ</t>
+  </si>
+  <si>
+    <t>Hiển thị chính xác: Tên người nhận, SĐT, Địa chỉ giao hàng và Phương thức thanh toán</t>
+  </si>
+  <si>
+    <t>TC_TRACK_018</t>
+  </si>
+  <si>
+    <t>Track_Product_List</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị Danh sách sản phẩm trong đơn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Tra cứu đơn "GF284910"
+2. Xem card Sản phẩm</t>
+  </si>
+  <si>
+    <t>Hiển thị đủ 3 sản phẩm: Tên, Phân loại/Đơn vị, Số lượng và Thành tiền từng món</t>
+  </si>
+  <si>
+    <t>TC_TRACK_019</t>
+  </si>
+  <si>
+    <t>Track_ShippingFee_Display</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị Phí vận chuyển trong chi tiết đơn</t>
+  </si>
+  <si>
+    <t>1. Xem dòng Phí vận chuyển</t>
+  </si>
+  <si>
+    <t>Hiển thị đúng phí vận chuyển đã tính lúc đặt hàng (hoặc "Miễn phí" nếu đạt freeship)</t>
+  </si>
+  <si>
+    <t>TC_TRACK_020</t>
+  </si>
+  <si>
+    <t>Track_Total_Calculation</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị Tổng thanh toán</t>
+  </si>
+  <si>
+    <t>1. Tra cứu đơn "GF284910"</t>
+  </si>
+  <si>
+    <t>Tổng thanh toán = Tiền hàng (325.000đ) + Phí ship (15.000đ) = 340.000đ</t>
+  </si>
+  <si>
+    <t>TC_TRACK_021</t>
+  </si>
+  <si>
+    <t>Track_API_Call</t>
+  </si>
+  <si>
+    <t>Gọi API tra cứu Backend thực tế</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập mã đơn
+2. Bấm Tra cứu</t>
+  </si>
+  <si>
+    <t>GET /api/orders/tracking/{code}</t>
+  </si>
+  <si>
+    <t>Dữ liệu đơn hàng được trả về từ Backend Laravel CSDL MySQL</t>
+  </si>
+  <si>
+    <t>TC_TRACK_022</t>
+  </si>
+  <si>
+    <t>Track_Loading_State</t>
+  </si>
+  <si>
+    <t>Kiểm tra trạng thái Đang tải khi tra cứu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhấn nút Tra cứu
+2. Quan sát nút</t>
+  </si>
+  <si>
+    <t>Nút chuyển sang icon xoay vòng (Spinner) và chữ "Đang tìm..."</t>
+  </si>
+  <si>
+    <t>TC_TRACK_023</t>
+  </si>
+  <si>
+    <t>Track_SpecialChar_Search</t>
+  </si>
+  <si>
+    <t>Tra cứu mã đơn chứa ký tự đặc biệt nguy hiểm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập: "GF&lt;script&gt;"
+2. Bấm Tra cứu</t>
+  </si>
+  <si>
+    <t>Mã chứa XSS</t>
+  </si>
+  <si>
+    <t>Xử lý an toàn, báo không tìm thấy mã đơn, không bị lỗi script</t>
+  </si>
+  <si>
+    <t>TC_TRACK_024</t>
+  </si>
+  <si>
+    <t>Track_Responsive_Mobile</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị Timeline trên màn hình điện thoại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Bật F12 375px
+2. Xem Timeline</t>
+  </si>
+  <si>
+    <t>Timeline chuyển sang dạng danh sách dọc dễ nhìn, đầy đủ icon trạng thái</t>
+  </si>
+  <si>
+    <t>TC_TRACK_025</t>
+  </si>
+  <si>
+    <t>Track_CopyCode_Flow</t>
+  </si>
+  <si>
+    <t>Tra cứu bằng mã đơn vừa tạo mới từ Checkout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Đặt hàng mới tại /checkout lấy mã
+2. Vào /tracking tra cứu mã đó</t>
+  </si>
+  <si>
+    <t>Mã đơn mới</t>
+  </si>
+  <si>
+    <t>Tra cứu thành công đơn hàng vừa tạo trong CSDL</t>
+  </si>
+  <si>
+    <t>TC_TRACK_026</t>
+  </si>
+  <si>
+    <t>Track_Cancelled_Badge</t>
+  </si>
+  <si>
+    <t>Hiển thị trạng thái khi đơn hàng bị Hủy</t>
+  </si>
+  <si>
+    <t>1. Tra cứu đơn hàng bị hủy</t>
+  </si>
+  <si>
+    <t>Status: Cancelled</t>
+  </si>
+  <si>
+    <t>Badge đỏ "Đã hủy" hiển thị rõ ràng</t>
+  </si>
+  <si>
+    <t>Kiểm Thử REST API Backend Laravel</t>
+  </si>
+  <si>
+    <t>Backend Laravel đang chạy trên cổng 8000 (http://127.0.0.1:8000).</t>
+  </si>
+  <si>
+    <t>TC_API_001</t>
+  </si>
+  <si>
+    <t>API_Categories_List</t>
+  </si>
+  <si>
+    <t>Lấy danh sách toàn bộ Danh mục nông sản</t>
+  </si>
+  <si>
+    <t>GET /api/categories</t>
+  </si>
+  <si>
+    <t>Headers: Accept: application/json</t>
+  </si>
+  <si>
+    <t>Trả về HTTP 200, JSON success: true kèm mảng 5 danh mục có đếm số sản phẩm</t>
+  </si>
+  <si>
+    <t>TC_API_002</t>
+  </si>
+  <si>
+    <t>API_Categories_Detail</t>
+  </si>
+  <si>
+    <t>Lấy chi tiết 1 danh mục theo Slug hợp lệ</t>
+  </si>
+  <si>
+    <t>GET /api/categories/trai-cay</t>
+  </si>
+  <si>
+    <t>Slug: trai-cay</t>
+  </si>
+  <si>
+    <t>Trả về HTTP 200, JSON thông tin danh mục "Trái cây tươi ngon"</t>
+  </si>
+  <si>
+    <t>TC_API_003</t>
+  </si>
+  <si>
+    <t>API_Categories_NotFound</t>
+  </si>
+  <si>
+    <t>Lấy danh mục theo Slug không tồn tại</t>
+  </si>
+  <si>
+    <t>GET /api/categories/danh-muc-la</t>
+  </si>
+  <si>
+    <t>Slug: danh-muc-la</t>
+  </si>
+  <si>
+    <t>Trả về HTTP 404, JSON success: false, message: "Danh mục không tồn tại"</t>
+  </si>
+  <si>
+    <t>TC_API_004</t>
+  </si>
+  <si>
+    <t>API_Products_List</t>
+  </si>
+  <si>
+    <t>Lấy danh sách tất cả Sản phẩm</t>
+  </si>
+  <si>
+    <t>GET /api/products</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Trả về HTTP 200, JSON count: 12, kèm mảng đầy đủ thông tin sản phẩm và variants</t>
+  </si>
+  <si>
+    <t>TC_API_005</t>
+  </si>
+  <si>
+    <t>API_Products_FilterCat</t>
+  </si>
+  <si>
+    <t>Lọc sản phẩm theo Category Slug</t>
+  </si>
+  <si>
+    <t>GET /api/products?category=tra-ca-phe</t>
+  </si>
+  <si>
+    <t>Param: category=tra-ca-phe</t>
+  </si>
+  <si>
+    <t>Trả về HTTP 200, chỉ gồm các sản phẩm trà và cà phê</t>
+  </si>
+  <si>
+    <t>TC_API_006</t>
+  </si>
+  <si>
+    <t>API_Products_Search</t>
+  </si>
+  <si>
+    <t>Tìm kiếm sản phẩm theo từ khóa</t>
+  </si>
+  <si>
+    <t>GET /api/products?search=sau+rieng</t>
+  </si>
+  <si>
+    <t>Param: search=sau riêng</t>
+  </si>
+  <si>
+    <t>Trả về HTTP 200, danh sách chứa sản phẩm Sầu riêng</t>
+  </si>
+  <si>
+    <t>TC_API_007</t>
+  </si>
+  <si>
+    <t>API_Products_SortPriceAsc</t>
+  </si>
+  <si>
+    <t>Sắp xếp sản phẩm theo giá tăng dần</t>
+  </si>
+  <si>
+    <t>GET /api/products?sort=price-asc</t>
+  </si>
+  <si>
+    <t>Param: sort=price-asc</t>
+  </si>
+  <si>
+    <t>Trả về HTTP 200, sản phẩm đầu tiên có giá thấp nhất</t>
+  </si>
+  <si>
+    <t>TC_API_008</t>
+  </si>
+  <si>
+    <t>API_Products_Detail</t>
+  </si>
+  <si>
+    <t>Lấy chi tiết sản phẩm theo Slug</t>
+  </si>
+  <si>
+    <t>GET /api/products/sau-rieng-ri6</t>
+  </si>
+  <si>
+    <t>Slug: sau-rieng-ri6</t>
+  </si>
+  <si>
+    <t>Trả về HTTP 200, thông tin chi tiết kèm variants và mảng related products</t>
+  </si>
+  <si>
+    <t>TC_API_009</t>
+  </si>
+  <si>
+    <t>API_Products_DetailNotFound</t>
+  </si>
+  <si>
+    <t>Lấy chi tiết sản phẩm với Slug không tồn tại</t>
+  </si>
+  <si>
+    <t>GET /api/products/san-pham-xyz</t>
+  </si>
+  <si>
+    <t>Slug: san-pham-xyz</t>
+  </si>
+  <si>
+    <t>Trả về HTTP 404, JSON success: false</t>
+  </si>
+  <si>
+    <t>TC_API_010</t>
+  </si>
+  <si>
+    <t>API_Farmers_List</t>
+  </si>
+  <si>
+    <t>Lấy danh sách Nông hộ kèm tọa độ GIS</t>
+  </si>
+  <si>
+    <t>Trả về HTTP 200, count: 6, mỗi item có đầy đủ latitude &amp; longitude dạng float</t>
+  </si>
+  <si>
+    <t>TC_API_011</t>
+  </si>
+  <si>
+    <t>API_Farmers_FilterZone</t>
+  </si>
+  <si>
+    <t>Lọc nông hộ theo vùng miền</t>
+  </si>
+  <si>
+    <t>GET /api/farmers?zone=north</t>
+  </si>
+  <si>
+    <t>Param: zone=north</t>
+  </si>
+  <si>
+    <t>Trả về HTTP 200, chỉ gồm các nông hộ miền Bắc (Mộc Châu, Thái Nguyên)</t>
+  </si>
+  <si>
+    <t>TC_API_012</t>
+  </si>
+  <si>
+    <t>API_Shipping_List</t>
+  </si>
+  <si>
+    <t>Lấy danh sách Vùng giao hàng</t>
+  </si>
+  <si>
+    <t>Trả về HTTP 200, mảng 6 vùng giao hàng với đầy đủ base_fee và free_ship_minimum</t>
+  </si>
+  <si>
+    <t>TC_API_013</t>
+  </si>
+  <si>
+    <t>API_Shipping_Create_Valid</t>
+  </si>
+  <si>
+    <t>Thêm mới vùng giao hàng qua API</t>
+  </si>
+  <si>
+    <t>POST /api/shipping-zones</t>
+  </si>
+  <si>
+    <t>JSON Body: name, provinces, base_fee, extra_fee_per_kg, estimated_days</t>
+  </si>
+  <si>
+    <t>Trả về HTTP 201 Created, JSON thông tin vùng mới tạo với mã SZxxx</t>
+  </si>
+  <si>
+    <t>TC_API_014</t>
+  </si>
+  <si>
+    <t>API_Shipping_Create_Invalid</t>
+  </si>
+  <si>
+    <t>Thêm vùng giao hàng thiếu trường bắt buộc</t>
+  </si>
+  <si>
+    <t>JSON Body: thiếu name, base_fee âm</t>
+  </si>
+  <si>
+    <t>Trả về HTTP 422 Unprocessable Entity, JSON danh sách lỗi validation</t>
+  </si>
+  <si>
+    <t>TC_API_015</t>
+  </si>
+  <si>
+    <t>API_Shipping_Update</t>
+  </si>
+  <si>
+    <t>Cập nhật vùng giao hàng qua API</t>
+  </si>
+  <si>
+    <t>PUT /api/shipping-zones/SZ001</t>
+  </si>
+  <si>
+    <t>JSON Body: base_fee = 20000</t>
+  </si>
+  <si>
+    <t>Trả về HTTP 200, thông tin vùng sau khi cập nhật</t>
+  </si>
+  <si>
+    <t>TC_API_016</t>
+  </si>
+  <si>
+    <t>API_Shipping_Delete</t>
+  </si>
+  <si>
+    <t>Xóa vùng giao hàng qua API</t>
+  </si>
+  <si>
+    <t>DELETE /api/shipping-zones/SZ006</t>
+  </si>
+  <si>
+    <t>Param: id=SZ006</t>
+  </si>
+  <si>
+    <t>Trả về HTTP 200, message: "Đã xóa vùng giao hàng thành công!"</t>
+  </si>
+  <si>
+    <t>TC_API_017</t>
+  </si>
+  <si>
+    <t>API_Orders_Create_Valid</t>
+  </si>
+  <si>
+    <t>Tạo đơn hàng mới qua API</t>
+  </si>
+  <si>
+    <t>POST /api/orders</t>
+  </si>
+  <si>
+    <t>JSON Body: customer_name, phone, address, zone_id, payment_method, items</t>
+  </si>
+  <si>
+    <t>Trả về HTTP 201 Created, tracking_number dạng GFxxxxxx</t>
+  </si>
+  <si>
+    <t>TC_API_018</t>
+  </si>
+  <si>
+    <t>API_Orders_Track_Valid</t>
+  </si>
+  <si>
+    <t>Tra cứu đơn hàng qua API theo mã đơn</t>
+  </si>
+  <si>
+    <t>GET /api/orders/tracking/GF284910</t>
+  </si>
+  <si>
+    <t>Param: trackingNumber=GF284910</t>
+  </si>
+  <si>
+    <t>Trả về HTTP 200, thông tin đơn, danh sách items, timeline 4 bước và vị trí shipper</t>
+  </si>
+  <si>
+    <t>TC_API_019</t>
+  </si>
+  <si>
+    <t>API_Orders_Track_NotFound</t>
+  </si>
+  <si>
+    <t>Tra cứu mã đơn không tồn tại qua API</t>
+  </si>
+  <si>
+    <t>GET /api/orders/tracking/GF000000</t>
+  </si>
+  <si>
+    <t>Param: trackingNumber=GF000000</t>
+  </si>
+  <si>
+    <t>Trả về HTTP 404, message: "Không tìm thấy đơn hàng #GF000000"</t>
+  </si>
+  <si>
+    <t>TC_API_020</t>
+  </si>
+  <si>
+    <t>API_CORS_Headers</t>
+  </si>
+  <si>
+    <t>Kiểm tra Header CORS cho phép Next.js</t>
+  </si>
+  <si>
+    <t>OPTIONS /api/products</t>
+  </si>
+  <si>
+    <t>Header Origin: http://localhost:3000</t>
+  </si>
+  <si>
+    <t>Trả về Access-Control-Allow-Origin: http://localhost:3000</t>
   </si>
   <si>
     <t>Pass</t>
@@ -1155,13 +2521,13 @@
     <t>Số lượng TC</t>
   </si>
   <si>
-    <t>Phí Giao Hàng (CRUD)</t>
+    <t>Phí Giao Hàng (CRUD &amp; Validation)</t>
   </si>
   <si>
     <t>Thanh Toán &amp; Tính Phí Ship</t>
   </si>
   <si>
-    <t>Theo Dõi Hành Trình Giao Hàng</t>
+    <t>Theo Dõi Hành Trình Đơn Hàng</t>
   </si>
   <si>
     <t>TỔNG CỘNG</t>
@@ -1604,15 +2970,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
-    <col min="4" max="4" width="45" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="45" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
     <col min="9" max="10" width="14" customWidth="1"/>
@@ -1667,7 +3033,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
@@ -1699,7 +3065,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>22</v>
       </c>
@@ -1713,30 +3079,30 @@
         <v>25</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>29</v>
@@ -1751,24 +3117,24 @@
         <v>32</v>
       </c>
       <c r="G7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>35</v>
@@ -1783,24 +3149,24 @@
         <v>38</v>
       </c>
       <c r="G8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>41</v>
@@ -1815,7 +3181,7 @@
         <v>44</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>21</v>
@@ -1827,515 +3193,867 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="H10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="F13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" ht="52" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="G27" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E20" s="5" t="s">
+      <c r="H27" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E23" s="5" t="s">
+      <c r="F30" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J25" s="4" t="s">
+      <c r="F31" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2347,15 +4065,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
-    <col min="4" max="4" width="45" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="45" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
     <col min="9" max="10" width="14" customWidth="1"/>
@@ -2366,7 +4084,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>137</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2374,7 +4092,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>138</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2410,24 +4128,24 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>139</v>
+        <v>208</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>140</v>
+        <v>209</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>141</v>
+        <v>210</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>20</v>
@@ -2442,27 +4160,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>146</v>
+        <v>215</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>148</v>
+        <v>217</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>149</v>
+        <v>218</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>21</v>
@@ -2474,24 +4192,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>152</v>
+        <v>221</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>153</v>
+        <v>222</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>154</v>
+        <v>223</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>155</v>
+        <v>224</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>20</v>
@@ -2506,24 +4224,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>157</v>
+        <v>226</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>158</v>
+        <v>227</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>159</v>
+        <v>228</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>160</v>
+        <v>229</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>161</v>
+        <v>230</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>20</v>
@@ -2538,24 +4256,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>162</v>
+        <v>231</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>163</v>
+        <v>232</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>164</v>
+        <v>233</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>165</v>
+        <v>234</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>167</v>
+        <v>236</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>20</v>
@@ -2570,27 +4288,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>168</v>
+        <v>237</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>169</v>
+        <v>238</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>170</v>
+        <v>239</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>171</v>
+        <v>240</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>172</v>
+        <v>241</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>173</v>
+        <v>242</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>21</v>
@@ -2602,24 +4320,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>174</v>
+        <v>243</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>175</v>
+        <v>244</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>177</v>
+        <v>246</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>178</v>
+        <v>247</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>179</v>
+        <v>242</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>20</v>
@@ -2634,24 +4352,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>181</v>
+        <v>249</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>183</v>
+        <v>251</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>185</v>
+        <v>253</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>20</v>
@@ -2666,27 +4384,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>187</v>
+        <v>255</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>189</v>
+        <v>257</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>190</v>
+        <v>258</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>191</v>
+        <v>253</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>21</v>
@@ -2698,27 +4416,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>192</v>
+        <v>259</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>193</v>
+        <v>260</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>194</v>
+        <v>261</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>195</v>
+        <v>262</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>196</v>
+        <v>263</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>197</v>
+        <v>264</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>21</v>
@@ -2730,27 +4448,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>198</v>
+        <v>265</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>199</v>
+        <v>266</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>201</v>
+        <v>268</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>202</v>
+        <v>269</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>21</v>
@@ -2762,24 +4480,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>204</v>
+        <v>271</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>205</v>
+        <v>272</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>206</v>
+        <v>273</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>207</v>
+        <v>274</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>208</v>
+        <v>275</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>209</v>
+        <v>276</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>20</v>
@@ -2794,99 +4512,579 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>210</v>
+        <v>277</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>211</v>
+        <v>278</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>212</v>
+        <v>279</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>213</v>
+        <v>280</v>
       </c>
       <c r="E17" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" ht="52" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="E18" s="5" t="s">
+      <c r="F27" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="E19" s="5" t="s">
+      <c r="F28" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" s="4" t="s">
+      <c r="F29" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2898,15 +5096,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
-    <col min="4" max="4" width="45" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="45" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
     <col min="9" max="10" width="14" customWidth="1"/>
@@ -2917,7 +5115,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>225</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2925,7 +5123,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>226</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2961,24 +5159,24 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>227</v>
+        <v>382</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>228</v>
+        <v>383</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>229</v>
+        <v>384</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>230</v>
+        <v>385</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>231</v>
+        <v>386</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>20</v>
@@ -2993,24 +5191,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>232</v>
+        <v>387</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>233</v>
+        <v>388</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>234</v>
+        <v>389</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>235</v>
+        <v>390</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>236</v>
+        <v>391</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>20</v>
@@ -3025,27 +5223,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>237</v>
+        <v>392</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>238</v>
+        <v>393</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>239</v>
+        <v>394</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>240</v>
+        <v>395</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>241</v>
+        <v>18</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>242</v>
+        <v>396</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>21</v>
@@ -3057,27 +5255,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>243</v>
+        <v>397</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>244</v>
+        <v>398</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>245</v>
+        <v>399</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>246</v>
+        <v>400</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>247</v>
+        <v>401</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>248</v>
+        <v>402</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>21</v>
@@ -3089,27 +5287,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>249</v>
+        <v>403</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>250</v>
+        <v>404</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>251</v>
+        <v>405</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>252</v>
+        <v>406</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>253</v>
+        <v>407</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>254</v>
+        <v>408</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>21</v>
@@ -3121,27 +5319,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>255</v>
+        <v>409</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>256</v>
+        <v>410</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>257</v>
+        <v>411</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>30</v>
+        <v>412</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>258</v>
+        <v>18</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>259</v>
+        <v>413</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>21</v>
@@ -3153,24 +5351,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>260</v>
+        <v>414</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>261</v>
+        <v>415</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>262</v>
+        <v>416</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>263</v>
+        <v>417</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>264</v>
+        <v>418</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>265</v>
+        <v>419</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>20</v>
@@ -3185,27 +5383,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>266</v>
+        <v>420</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>267</v>
+        <v>421</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>268</v>
+        <v>422</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>269</v>
+        <v>423</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>270</v>
+        <v>18</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>271</v>
+        <v>424</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>21</v>
@@ -3217,24 +5415,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>272</v>
+        <v>425</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>273</v>
+        <v>426</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>274</v>
+        <v>427</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>275</v>
+        <v>428</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>276</v>
+        <v>429</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>277</v>
+        <v>430</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>20</v>
@@ -3249,27 +5447,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>278</v>
+        <v>431</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>279</v>
+        <v>432</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>280</v>
+        <v>433</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>281</v>
+        <v>434</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>282</v>
+        <v>37</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>283</v>
+        <v>435</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>21</v>
@@ -3281,27 +5479,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>284</v>
+        <v>436</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>285</v>
+        <v>437</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>286</v>
+        <v>438</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>287</v>
+        <v>439</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>288</v>
+        <v>440</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>289</v>
+        <v>441</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>21</v>
@@ -3313,35 +5511,547 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>290</v>
+        <v>442</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>291</v>
+        <v>443</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>292</v>
+        <v>444</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>293</v>
+        <v>445</v>
       </c>
       <c r="E16" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" s="4" t="s">
+      <c r="F23" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3353,15 +6063,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
-    <col min="4" max="4" width="45" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="45" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
     <col min="9" max="10" width="14" customWidth="1"/>
@@ -3372,7 +6082,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>295</v>
+        <v>537</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -3380,7 +6090,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>296</v>
+        <v>538</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3416,24 +6126,24 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>297</v>
+        <v>539</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>298</v>
+        <v>540</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>299</v>
+        <v>541</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>300</v>
+        <v>542</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>301</v>
+        <v>543</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>20</v>
@@ -3448,27 +6158,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>302</v>
+        <v>544</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>303</v>
+        <v>545</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>304</v>
+        <v>546</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>305</v>
+        <v>547</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>306</v>
+        <v>548</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>307</v>
+        <v>549</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>21</v>
@@ -3480,27 +6190,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>308</v>
+        <v>550</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>309</v>
+        <v>551</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>310</v>
+        <v>552</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>311</v>
+        <v>553</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>312</v>
+        <v>554</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>313</v>
+        <v>555</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>21</v>
@@ -3512,24 +6222,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>314</v>
+        <v>556</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>315</v>
+        <v>557</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>316</v>
+        <v>558</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>317</v>
+        <v>559</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>318</v>
+        <v>560</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>319</v>
+        <v>561</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>20</v>
@@ -3544,24 +6254,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>320</v>
+        <v>562</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>321</v>
+        <v>563</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>322</v>
+        <v>564</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>323</v>
+        <v>565</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>318</v>
+        <v>566</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>324</v>
+        <v>567</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>20</v>
@@ -3576,27 +6286,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>325</v>
+        <v>568</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>326</v>
+        <v>569</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>327</v>
+        <v>570</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>328</v>
+        <v>571</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>318</v>
+        <v>572</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>329</v>
+        <v>573</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>21</v>
@@ -3608,27 +6318,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>330</v>
+        <v>574</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>331</v>
+        <v>575</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>332</v>
+        <v>576</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>333</v>
+        <v>577</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>334</v>
+        <v>578</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>335</v>
+        <v>579</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>21</v>
@@ -3640,27 +6350,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>336</v>
+        <v>580</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>337</v>
+        <v>581</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>338</v>
+        <v>582</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>339</v>
+        <v>583</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>340</v>
+        <v>584</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>341</v>
+        <v>585</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>21</v>
@@ -3672,24 +6382,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>342</v>
+        <v>586</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>343</v>
+        <v>587</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>344</v>
+        <v>588</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>345</v>
+        <v>589</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>346</v>
+        <v>590</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>347</v>
+        <v>591</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>20</v>
@@ -3704,27 +6414,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>348</v>
+        <v>592</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>349</v>
+        <v>593</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>350</v>
+        <v>594</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>351</v>
+        <v>595</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>352</v>
+        <v>554</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>353</v>
+        <v>596</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>21</v>
@@ -3733,6 +6443,518 @@
         <v>21</v>
       </c>
       <c r="J14" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>629</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>650</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>664</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>675</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>678</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>679</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>682</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3744,10 +6966,721 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>689</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>692</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>693</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>694</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>695</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>696</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>698</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>705</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>706</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>707</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>708</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>711</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>712</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>719</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>720</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>723</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>724</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>725</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>726</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>728</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>729</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>730</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>731</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>736</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>740</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>741</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>707</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>746</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>750</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>707</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>760</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>761</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>767</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>772</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>774</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>777</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>781</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>783</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>798</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="5" width="15" customWidth="1"/>
   </cols>
@@ -3757,21 +7690,21 @@
         <v>21</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>354</v>
+        <v>800</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>355</v>
+        <v>801</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>356</v>
+        <v>802</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>357</v>
+        <v>803</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>358</v>
+        <v>804</v>
       </c>
       <c r="B2" s="8">
         <v>0</v>
@@ -3783,12 +7716,12 @@
         <v>0</v>
       </c>
       <c r="E2" s="8">
-        <v>58</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>359</v>
+        <v>805</v>
       </c>
       <c r="B3" s="8">
         <v>0</v>
@@ -3800,12 +7733,12 @@
         <v>0</v>
       </c>
       <c r="E3" s="8">
-        <v>58</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>360</v>
+        <v>806</v>
       </c>
       <c r="B4" s="8">
         <v>0</v>
@@ -3817,56 +7750,64 @@
         <v>0</v>
       </c>
       <c r="E4" s="8">
-        <v>58</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>361</v>
+        <v>807</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>362</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>363</v>
+        <v>809</v>
       </c>
       <c r="B7" s="8">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>364</v>
+        <v>810</v>
       </c>
       <c r="B8" s="8">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>225</v>
+        <v>380</v>
       </c>
       <c r="B9" s="8">
-        <v>12</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>365</v>
+        <v>811</v>
       </c>
       <c r="B10" s="8">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="B11" s="13">
-        <v>58</v>
+      <c r="A11" s="11" t="s">
+        <v>683</v>
+      </c>
+      <c r="B11" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>812</v>
+      </c>
+      <c r="B12" s="13">
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/greenfood/testcases/Test_Cases_GreenFood_Duong.xlsx
+++ b/greenfood/testcases/Test_Cases_GreenFood_Duong.xlsx
@@ -4,60 +4,900 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Phí Giao Hàng" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Thanh Toán" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Bản Đồ GIS" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Theo Dõi Giao Hàng" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="API Backend" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Kết quả tổng hợp" state="visible" r:id="rId9"/>
+    <sheet sheetId="1" name="Sản Phẩm" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Nông Hộ" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Khách Hàng" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Đơn Hàng" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Cài Đặt" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Phí Giao Hàng" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Thanh Toán" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Bản Đồ GIS" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Theo Dõi Giao Hàng" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="API Backend" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Kết quả tổng hợp" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1973" uniqueCount="1084">
   <si>
     <t>Tên chức năng</t>
   </si>
   <si>
+    <t>Quản Lý Sản Phẩm - CRUD</t>
+  </si>
+  <si>
+    <t>Precondition</t>
+  </si>
+  <si>
+    <t>Admin đã đăng nhập, mở trang Sản phẩm.</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Test case Name</t>
+  </si>
+  <si>
+    <t>Test step</t>
+  </si>
+  <si>
+    <t>Test data</t>
+  </si>
+  <si>
+    <t>Expected result</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Actual result</t>
+  </si>
+  <si>
+    <t>Test result</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>TC_PROD_001</t>
+  </si>
+  <si>
+    <t>Product_List</t>
+  </si>
+  <si>
+    <t>Kiểm tra giao diện trang Quản Lý Sản Phẩm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Truy cập trang Sản phẩm
+2. Quan sát</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Hiển thị tiêu đề, ô tìm kiếm, nút Thêm mới, bảng danh sách sản phẩm</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Hiển thị tiêu đề, ô tìm kiếm, nút Thêm mới, bảng danh sách</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>19/08/2026</t>
+  </si>
+  <si>
+    <t>TC_PROD_002</t>
+  </si>
+  <si>
+    <t>Product_Search</t>
+  </si>
+  <si>
+    <t>Tìm kiếm sản phẩm với từ khóa hợp lệ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập tên sản phẩm
+2. Nhấn Enter</t>
+  </si>
+  <si>
+    <t>Từ khóa: "Sầu riêng"</t>
+  </si>
+  <si>
+    <t>Danh sách hiển thị đúng các sản phẩm chứa từ khóa</t>
+  </si>
+  <si>
+    <t>TC_PROD_003</t>
+  </si>
+  <si>
+    <t>Tìm kiếm không có kết quả</t>
+  </si>
+  <si>
+    <t>1. Nhập từ khóa không tồn tại</t>
+  </si>
+  <si>
+    <t>Từ khóa: "XYZ12345"</t>
+  </si>
+  <si>
+    <t>Bảng hiển thị trạng thái "Không có dữ liệu"</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>TC_PROD_004</t>
+  </si>
+  <si>
+    <t>Tìm kiếm với khoảng trắng đầu/cuối</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập từ khóa có khoảng trắng
+2. Tìm kiếm</t>
+  </si>
+  <si>
+    <t>Từ khóa: "   Sầu riêng   "</t>
+  </si>
+  <si>
+    <t>Hệ thống tự trim() và hiển thị kết quả đúng</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>TC_PROD_005</t>
+  </si>
+  <si>
+    <t>Tìm kiếm với ký tự đặc biệt</t>
+  </si>
+  <si>
+    <t>1. Nhập ký tự đặc biệt</t>
+  </si>
+  <si>
+    <t>Từ khóa: "!@#$%"</t>
+  </si>
+  <si>
+    <t>Không lỗi hệ thống, trả về danh sách trống hoặc kết quả phù hợp</t>
+  </si>
+  <si>
+    <t>Không lỗi hệ thống, trả về kết quả an toàn</t>
+  </si>
+  <si>
+    <t>TC_PROD_006</t>
+  </si>
+  <si>
+    <t>Product_Add_UI</t>
+  </si>
+  <si>
+    <t>Kiểm tra giao diện popup Thêm Sản Phẩm</t>
+  </si>
+  <si>
+    <t>1. Nhấn nút "Thêm Mới"</t>
+  </si>
+  <si>
+    <t>Popup hiển thị, các trường rỗng, có nút Lưu và Hủy</t>
+  </si>
+  <si>
+    <t>TC_PROD_007</t>
+  </si>
+  <si>
+    <t>Product_Add_Name</t>
+  </si>
+  <si>
+    <t>Để trống Tên Sản Phẩm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Để trống Tên
+2. Điền đủ các trường khác
+3. Bấm Lưu</t>
+  </si>
+  <si>
+    <t>Tên: (Empty)</t>
+  </si>
+  <si>
+    <t>Báo lỗi "Tên sản phẩm không được để trống"</t>
+  </si>
+  <si>
+    <t>TC_PROD_008</t>
+  </si>
+  <si>
+    <t>Tên Sản Phẩm rất dài</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập tên &gt; 255 ký tự
+2. Bấm Lưu</t>
+  </si>
+  <si>
+    <t>Tên: chuỗi 300 ký tự</t>
+  </si>
+  <si>
+    <t>Báo lỗi vượt quá ký tự cho phép hoặc cắt chuỗi hợp lý</t>
+  </si>
+  <si>
+    <t>Báo lỗi vượt quá ký tự cho phép</t>
+  </si>
+  <si>
+    <t>TC_PROD_009</t>
+  </si>
+  <si>
+    <t>Product_Add_Price</t>
+  </si>
+  <si>
+    <t>Để trống Giá Bán</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Để trống Giá
+2. Điền đủ các trường khác
+3. Bấm Lưu</t>
+  </si>
+  <si>
+    <t>Giá: (Empty)</t>
+  </si>
+  <si>
+    <t>Báo lỗi bắt buộc nhập giá</t>
+  </si>
+  <si>
+    <t>TC_PROD_010</t>
+  </si>
+  <si>
+    <t>Giá Bán là số âm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập số âm
+2. Bấm Lưu</t>
+  </si>
+  <si>
+    <t>Giá: -50000</t>
+  </si>
+  <si>
+    <t>Hệ thống chặn, báo lỗi giá trị không hợp lệ</t>
+  </si>
+  <si>
+    <t>TC_PROD_011</t>
+  </si>
+  <si>
+    <t>Giá Bán nhập chữ/ký tự</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập chữ vào ô Giá
+2. Bấm Lưu</t>
+  </si>
+  <si>
+    <t>Giá: "abc"</t>
+  </si>
+  <si>
+    <t>Không cho phép nhập chữ hoặc báo lỗi validate</t>
+  </si>
+  <si>
+    <t>TC_PROD_012</t>
+  </si>
+  <si>
+    <t>Product_Add_Stock</t>
+  </si>
+  <si>
+    <t>Số lượng tồn kho là số âm</t>
+  </si>
+  <si>
+    <t>Tồn kho: -10</t>
+  </si>
+  <si>
+    <t>Báo lỗi số lượng không được âm</t>
+  </si>
+  <si>
+    <t>TC_PROD_013</t>
+  </si>
+  <si>
+    <t>Product_Add_Category</t>
+  </si>
+  <si>
+    <t>Không chọn Danh mục</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Bỏ qua dropdown danh mục
+2. Bấm Lưu</t>
+  </si>
+  <si>
+    <t>Danh mục: Chưa chọn</t>
+  </si>
+  <si>
+    <t>Báo lỗi chưa chọn danh mục</t>
+  </si>
+  <si>
+    <t>TC_PROD_014</t>
+  </si>
+  <si>
+    <t>Product_Add_Valid</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm hợp lệ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Điền đủ thông tin chuẩn
+2. Nhấn Lưu</t>
+  </si>
+  <si>
+    <t>Tên: Xoài, Giá: 100k, Tồn: 50, Danh mục: Trái cây</t>
+  </si>
+  <si>
+    <t>Lưu thành công, thông báo xanh, popup đóng, hiện trên list</t>
+  </si>
+  <si>
+    <t>TC_PROD_015</t>
+  </si>
+  <si>
+    <t>Product_Add_MultiClick</t>
+  </si>
+  <si>
+    <t>Nhấn Lưu nhiều lần liên tiếp (Rapid click)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Điền đủ thông tin
+2. Nhấn đúp thật nhanh nút Lưu</t>
+  </si>
+  <si>
+    <t>Data hợp lệ</t>
+  </si>
+  <si>
+    <t>Chỉ tạo ra 1 bản ghi duy nhất</t>
+  </si>
+  <si>
+    <t>TC_PROD_016</t>
+  </si>
+  <si>
+    <t>Product_Add_Cancel</t>
+  </si>
+  <si>
+    <t>Nhấn nút Hủy Bỏ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Mở popup, nhập data
+2. Nhấn Hủy Bỏ</t>
+  </si>
+  <si>
+    <t>Data nhập</t>
+  </si>
+  <si>
+    <t>Popup đóng, không lưu dữ liệu</t>
+  </si>
+  <si>
+    <t>TC_PROD_017</t>
+  </si>
+  <si>
+    <t>Product_Edit_UI</t>
+  </si>
+  <si>
+    <t>Kiểm tra popup Chỉnh Sửa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Chọn sản phẩm A
+2. Nhấn Sửa</t>
+  </si>
+  <si>
+    <t>Dữ liệu của sản phẩm A được đổ đầy đủ vào form</t>
+  </si>
+  <si>
+    <t>TC_PROD_018</t>
+  </si>
+  <si>
+    <t>Product_Edit_Name</t>
+  </si>
+  <si>
+    <t>Xóa tên sản phẩm khi sửa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Xóa nội dung ở Tên
+2. Lưu</t>
+  </si>
+  <si>
+    <t>Tên: (Rỗng)</t>
+  </si>
+  <si>
+    <t>Báo lỗi bắt buộc nhập tên</t>
+  </si>
+  <si>
+    <t>TC_PROD_019</t>
+  </si>
+  <si>
+    <t>Product_Edit_Valid</t>
+  </si>
+  <si>
+    <t>Cập nhật sản phẩm thành công</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Đổi giá bán và danh mục
+2. Lưu</t>
+  </si>
+  <si>
+    <t>Giá: 120k</t>
+  </si>
+  <si>
+    <t>Cập nhật thành công, list tự refresh</t>
+  </si>
+  <si>
+    <t>TC_PROD_020</t>
+  </si>
+  <si>
+    <t>Product_Del_UI</t>
+  </si>
+  <si>
+    <t>Kiểm tra popup Xóa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Chọn Xóa
+2. Quan sát</t>
+  </si>
+  <si>
+    <t>Hiển thị cảnh báo xác nhận xóa đúng tên sản phẩm</t>
+  </si>
+  <si>
+    <t>TC_PROD_021</t>
+  </si>
+  <si>
+    <t>Product_Del_Confirm</t>
+  </si>
+  <si>
+    <t>Xác nhận Xóa sản phẩm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhấn Xóa
+2. Xác nhận</t>
+  </si>
+  <si>
+    <t>Sản phẩm test</t>
+  </si>
+  <si>
+    <t>Bản ghi biến mất khỏi danh sách, báo thành công</t>
+  </si>
+  <si>
+    <t>TC_PROD_022</t>
+  </si>
+  <si>
+    <t>Product_Del_Cancel</t>
+  </si>
+  <si>
+    <t>Hủy xóa sản phẩm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhấn Xóa
+2. Nhấn Hủy</t>
+  </si>
+  <si>
+    <t>Đóng popup, bản ghi vẫn còn</t>
+  </si>
+  <si>
+    <t>Quản Lý Nông Hộ - CRUD</t>
+  </si>
+  <si>
+    <t>Admin mở trang Quản lý Nông Hộ.</t>
+  </si>
+  <si>
+    <t>TC_FARM_001</t>
+  </si>
+  <si>
+    <t>Farmer_List</t>
+  </si>
+  <si>
+    <t>Kiểm tra danh sách Nông Hộ</t>
+  </si>
+  <si>
+    <t>1. Xem danh sách</t>
+  </si>
+  <si>
+    <t>Cột: Tên, Khu vực, Số SP, Trạng thái, Thao tác</t>
+  </si>
+  <si>
+    <t>TC_FARM_002</t>
+  </si>
+  <si>
+    <t>Farmer_Search</t>
+  </si>
+  <si>
+    <t>Tìm kiếm theo tên HTX/Nông trại</t>
+  </si>
+  <si>
+    <t>1. Nhập từ khóa</t>
+  </si>
+  <si>
+    <t>Từ khóa: "Mộc Châu"</t>
+  </si>
+  <si>
+    <t>Hiển thị đúng nông hộ</t>
+  </si>
+  <si>
+    <t>TC_FARM_003</t>
+  </si>
+  <si>
+    <t>Farmer_Add_UI</t>
+  </si>
+  <si>
+    <t>Kiểm tra popup thêm nông hộ</t>
+  </si>
+  <si>
+    <t>1. Nhấn Thêm Nông Hộ</t>
+  </si>
+  <si>
+    <t>Popup hiện ra đủ các trường</t>
+  </si>
+  <si>
+    <t>TC_FARM_004</t>
+  </si>
+  <si>
+    <t>Farmer_Add_Empty</t>
+  </si>
+  <si>
+    <t>Để trống các trường bắt buộc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Không nhập gì
+2. Lưu</t>
+  </si>
+  <si>
+    <t>Báo lỗi các trường: Tên, Khu vực</t>
+  </si>
+  <si>
+    <t>TC_FARM_005</t>
+  </si>
+  <si>
+    <t>Farmer_Add_Status</t>
+  </si>
+  <si>
+    <t>Kiểm tra Dropdown Trạng Thái</t>
+  </si>
+  <si>
+    <t>1. Mở danh sách trạng thái</t>
+  </si>
+  <si>
+    <t>Có 2 option: Đã xác minh, Chờ duyệt</t>
+  </si>
+  <si>
+    <t>TC_FARM_006</t>
+  </si>
+  <si>
+    <t>Farmer_Add_Valid</t>
+  </si>
+  <si>
+    <t>Thêm Nông Hộ thành công</t>
+  </si>
+  <si>
+    <t>1. Điền đủ và lưu</t>
+  </si>
+  <si>
+    <t>Tên: Farm A, KV: Đà Lạt</t>
+  </si>
+  <si>
+    <t>Thành công, hiển thị trên bảng</t>
+  </si>
+  <si>
+    <t>TC_FARM_007</t>
+  </si>
+  <si>
+    <t>Farmer_Edit_UI</t>
+  </si>
+  <si>
+    <t>Đổ dữ liệu khi sửa</t>
+  </si>
+  <si>
+    <t>1. Nhấn Sửa</t>
+  </si>
+  <si>
+    <t>Đổ đúng dữ liệu nông hộ đang chọn</t>
+  </si>
+  <si>
+    <t>TC_FARM_008</t>
+  </si>
+  <si>
+    <t>Farmer_Edit_Status</t>
+  </si>
+  <si>
+    <t>Cập nhật trạng thái nông hộ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Đổi "Chờ duyệt" -&gt; "Đã xác minh"
+2. Lưu</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Cập nhật thành công, list hiện màu badge tương ứng</t>
+  </si>
+  <si>
+    <t>TC_FARM_009</t>
+  </si>
+  <si>
+    <t>Farmer_Delete</t>
+  </si>
+  <si>
+    <t>Xóa Nông hộ</t>
+  </si>
+  <si>
+    <t>1. Nhấn Xóa và xác nhận</t>
+  </si>
+  <si>
+    <t>Xóa thành công, biến mất khỏi list</t>
+  </si>
+  <si>
+    <t>Quản Lý Khách Hàng</t>
+  </si>
+  <si>
+    <t>Admin mở trang Quản lý Khách Hàng.</t>
+  </si>
+  <si>
+    <t>TC_CUST_001</t>
+  </si>
+  <si>
+    <t>Customer_List</t>
+  </si>
+  <si>
+    <t>Kiểm tra danh sách Khách Hàng</t>
+  </si>
+  <si>
+    <t>1. Mở trang Khách Hàng</t>
+  </si>
+  <si>
+    <t>Hiển thị danh sách khách hàng gồm Tên, SĐT, Email, Tổng chi tiêu, Đơn hàng</t>
+  </si>
+  <si>
+    <t>Hiển thị danh sách khách hàng</t>
+  </si>
+  <si>
+    <t>TC_CUST_002</t>
+  </si>
+  <si>
+    <t>Customer_Search</t>
+  </si>
+  <si>
+    <t>Tìm kiếm khách hàng theo Tên/SĐT</t>
+  </si>
+  <si>
+    <t>1. Nhập SĐT vào ô tìm kiếm</t>
+  </si>
+  <si>
+    <t>Từ khóa: "0909123456"</t>
+  </si>
+  <si>
+    <t>Hiển thị đúng khách hàng khớp với SĐT</t>
+  </si>
+  <si>
+    <t>Hiển thị đúng khách hàng</t>
+  </si>
+  <si>
+    <t>TC_CUST_003</t>
+  </si>
+  <si>
+    <t>Customer_Filter</t>
+  </si>
+  <si>
+    <t>Lọc khách hàng theo Hạng thành viên</t>
+  </si>
+  <si>
+    <t>1. Chọn hạng VIP</t>
+  </si>
+  <si>
+    <t>Hạng: VIP</t>
+  </si>
+  <si>
+    <t>Chỉ hiển thị khách hàng hạng VIP</t>
+  </si>
+  <si>
+    <t>TC_CUST_004</t>
+  </si>
+  <si>
+    <t>Customer_Detail</t>
+  </si>
+  <si>
+    <t>Xem chi tiết lịch sử mua hàng của khách</t>
+  </si>
+  <si>
+    <t>1. Bấm vào 1 khách hàng</t>
+  </si>
+  <si>
+    <t>Popup/Trang chi tiết hiển thị lịch sử các đơn hàng đã mua</t>
+  </si>
+  <si>
+    <t>Hiển thị chi tiết lịch sử đơn hàng</t>
+  </si>
+  <si>
+    <t>TC_CUST_005</t>
+  </si>
+  <si>
+    <t>Customer_Status</t>
+  </si>
+  <si>
+    <t>Khóa / Mở khóa tài khoản khách hàng</t>
+  </si>
+  <si>
+    <t>1. Bấm đổi trạng thái tài khoản</t>
+  </si>
+  <si>
+    <t>Status: Block</t>
+  </si>
+  <si>
+    <t>Cập nhật trạng thái khóa tài khoản thành công</t>
+  </si>
+  <si>
+    <t>Cập nhật trạng thái thành công</t>
+  </si>
+  <si>
+    <t>Quản Lý Đơn Hàng Admin</t>
+  </si>
+  <si>
+    <t>Admin mở trang Quản lý Đơn Hàng.</t>
+  </si>
+  <si>
+    <t>TC_ORD_001</t>
+  </si>
+  <si>
+    <t>Order_List</t>
+  </si>
+  <si>
+    <t>Kiểm tra bảng danh sách Đơn Hàng</t>
+  </si>
+  <si>
+    <t>1. Mở trang Đơn Hàng</t>
+  </si>
+  <si>
+    <t>Hiển thị danh sách đơn: Mã đơn, Khách hàng, Tổng tiền, Trạng thái, Ngày tạo</t>
+  </si>
+  <si>
+    <t>Hiển thị danh sách đơn hàng</t>
+  </si>
+  <si>
+    <t>TC_ORD_002</t>
+  </si>
+  <si>
+    <t>Order_Search</t>
+  </si>
+  <si>
+    <t>Tìm kiếm đơn hàng theo Mã đơn</t>
+  </si>
+  <si>
+    <t>1. Nhập mã đơn "GF284910"</t>
+  </si>
+  <si>
+    <t>Mã: GF284910</t>
+  </si>
+  <si>
+    <t>Hiển thị đúng đơn hàng GF284910</t>
+  </si>
+  <si>
+    <t>Hiển thị đúng đơn hàng</t>
+  </si>
+  <si>
+    <t>TC_ORD_003</t>
+  </si>
+  <si>
+    <t>Order_Filter_Status</t>
+  </si>
+  <si>
+    <t>Lọc đơn hàng theo Trạng thái (Đang giao, Đã giao)</t>
+  </si>
+  <si>
+    <t>1. Chọn lọc "Đang giao"</t>
+  </si>
+  <si>
+    <t>Status: Shipping</t>
+  </si>
+  <si>
+    <t>Chỉ hiển thị các đơn hàng đang giao</t>
+  </si>
+  <si>
+    <t>Lọc đúng trạng thái</t>
+  </si>
+  <si>
+    <t>TC_ORD_004</t>
+  </si>
+  <si>
+    <t>Order_Update_Status</t>
+  </si>
+  <si>
+    <t>Cập nhật trạng thái đơn hàng (Xác nhận -&gt; Đang giao)</t>
+  </si>
+  <si>
+    <t>1. Đổi trạng thái đơn sang Đang giao</t>
+  </si>
+  <si>
+    <t>Cập nhật trạng thái thành công, thông báo cho khách</t>
+  </si>
+  <si>
+    <t>TC_ORD_005</t>
+  </si>
+  <si>
+    <t>Order_Cancel</t>
+  </si>
+  <si>
+    <t>Hủy đơn hàng và ghi nhận lý do</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Bấm Hủy đơn hàng
+2. Nhập lý do</t>
+  </si>
+  <si>
+    <t>Lý do: Khách đổi ý</t>
+  </si>
+  <si>
+    <t>Đơn chuyển sang trạng thái Đã hủy</t>
+  </si>
+  <si>
+    <t>Chuyển sang trạng thái Đã hủy</t>
+  </si>
+  <si>
+    <t>Cài Đặt Hệ Thống</t>
+  </si>
+  <si>
+    <t>Admin mở trang Cài Đặt.</t>
+  </si>
+  <si>
+    <t>TC_SET_001</t>
+  </si>
+  <si>
+    <t>Settings_UI</t>
+  </si>
+  <si>
+    <t>Kiểm tra trang Cài Đặt Hệ Thống</t>
+  </si>
+  <si>
+    <t>1. Mở trang Cài Đặt</t>
+  </si>
+  <si>
+    <t>Hiển thị các tab: Thông tin cửa hàng, Thanh toán, Vận chuyển, Tài khoản</t>
+  </si>
+  <si>
+    <t>Hiển thị các tab cài đặt</t>
+  </si>
+  <si>
+    <t>TC_SET_002</t>
+  </si>
+  <si>
+    <t>Settings_StoreInfo</t>
+  </si>
+  <si>
+    <t>Cập nhật Tên cửa hàng &amp; Hotline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Sửa Hotline: 028 7770 2614
+2. Lưu</t>
+  </si>
+  <si>
+    <t>Hotline mới</t>
+  </si>
+  <si>
+    <t>Lưu thông tin cửa hàng thành công</t>
+  </si>
+  <si>
+    <t>Lưu thông tin thành công</t>
+  </si>
+  <si>
+    <t>TC_SET_003</t>
+  </si>
+  <si>
+    <t>Settings_Password</t>
+  </si>
+  <si>
+    <t>Đổi mật khẩu tài khoản Admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập mật khẩu cũ &amp; mới
+2. Lưu</t>
+  </si>
+  <si>
+    <t>Pass mới</t>
+  </si>
+  <si>
+    <t>Đổi mật khẩu thành công</t>
+  </si>
+  <si>
     <t>Quản Lý Phí Giao Hàng - CRUD</t>
   </si>
   <si>
-    <t>Precondition</t>
-  </si>
-  <si>
     <t>Admin đã đăng nhập, mở trang Quản lý Phí Giao Hàng (/admin/shipping).</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Test case Name</t>
-  </si>
-  <si>
-    <t>Test step</t>
-  </si>
-  <si>
-    <t>Test data</t>
-  </si>
-  <si>
-    <t>Expected result</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>Actual result</t>
-  </si>
-  <si>
-    <t>Test result</t>
-  </si>
-  <si>
-    <t>Date</t>
   </si>
   <si>
     <t>TC_SHIP_001</t>
@@ -73,18 +913,9 @@
 2. Quan sát giao diện</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Hiển thị tiêu đề "Quản lý Phí Giao Hàng", ô tìm kiếm, nút "Thêm vùng mới", bảng danh sách các vùng</t>
   </si>
   <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>TC_SHIP_002</t>
   </si>
   <si>
@@ -154,9 +985,6 @@
     <t>Bảng hiển thị thông báo "Không tìm thấy vùng giao hàng nào!"</t>
   </si>
   <si>
-    <t>Medium</t>
-  </si>
-  <si>
     <t>TC_SHIP_006</t>
   </si>
   <si>
@@ -193,16 +1021,10 @@
     <t>Hệ thống tự trim khoảng trắng và hiển thị kết quả đúng</t>
   </si>
   <si>
-    <t>Low</t>
-  </si>
-  <si>
     <t>TC_SHIP_008</t>
   </si>
   <si>
     <t>Shipping_Search_SpecialChar</t>
-  </si>
-  <si>
-    <t>Tìm kiếm với ký tự đặc biệt</t>
   </si>
   <si>
     <t>1. Nhập ký tự đặc biệt vào ô search</t>
@@ -243,9 +1065,6 @@
 3. Bấm Lưu</t>
   </si>
   <si>
-    <t>Tên: (Empty)</t>
-  </si>
-  <si>
     <t>Báo lỗi "Tên vùng giao hàng không được để trống!"</t>
   </si>
   <si>
@@ -451,7 +1270,7 @@
 2. Bấm "Cập nhật"</t>
   </si>
   <si>
-    <t>Phí: 20000, TG: 1 ngày</t>
+    <t>Phí mới: 20000, TG: 1 ngày</t>
   </si>
   <si>
     <t>Toast thông báo thành công, bảng cập nhật giá trị mới lập tức</t>
@@ -2494,7 +3313,7 @@
     <t>Trả về Access-Control-Allow-Origin: http://localhost:3000</t>
   </si>
   <si>
-    <t>Pass</t>
+    <t/>
   </si>
   <si>
     <t>Fail</t>
@@ -2521,23 +3340,47 @@
     <t>Số lượng TC</t>
   </si>
   <si>
-    <t>Phí Giao Hàng (CRUD &amp; Validation)</t>
-  </si>
-  <si>
-    <t>Thanh Toán &amp; Tính Phí Ship</t>
-  </si>
-  <si>
-    <t>Theo Dõi Hành Trình Đơn Hàng</t>
-  </si>
-  <si>
-    <t>TỔNG CỘNG</t>
+    <t>Kết quả</t>
+  </si>
+  <si>
+    <t>Sản Phẩm (Admin CRUD)</t>
+  </si>
+  <si>
+    <t>100% PASS</t>
+  </si>
+  <si>
+    <t>Nông Hộ (Admin CRUD)</t>
+  </si>
+  <si>
+    <t>Khách Hàng (Admin)</t>
+  </si>
+  <si>
+    <t>Đơn Hàng (Admin)</t>
+  </si>
+  <si>
+    <t>Cài Đặt (Admin)</t>
+  </si>
+  <si>
+    <t>Phí Giao Hàng (Nhiệm vụ Dương)</t>
+  </si>
+  <si>
+    <t>Thanh Toán &amp; Tính Phí Ship (Nhiệm vụ Dương)</t>
+  </si>
+  <si>
+    <t>Tích Hợp Bản Đồ Nhà Vườn GIS (Nhiệm vụ Dương)</t>
+  </si>
+  <si>
+    <t>Theo Dõi Hành Trình Đơn Hàng (Nhiệm vụ Dương)</t>
+  </si>
+  <si>
+    <t>TỔNG CỘNG TOÀN HỆ THỐNG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -2551,6 +3394,12 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -2600,7 +3449,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2613,11 +3462,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2970,6 +3825,2697 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>949</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>950</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>951</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>952</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>953</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>953</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>955</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>956</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>957</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>958</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>959</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>959</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>961</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>962</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>964</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>965</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>965</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>967</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>968</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>969</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>970</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>971</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>971</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>973</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>974</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>975</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>976</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>977</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>977</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>978</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>979</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>980</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>981</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>982</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>983</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>983</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>985</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>986</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>987</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>988</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>989</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>989</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>991</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>992</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>993</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>994</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>995</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>995</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>997</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>998</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>781</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>970</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>1011</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>970</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>1015</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>1044</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>1044</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>1050</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>1062</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="3" width="18" customWidth="1"/>
+    <col min="4" max="5" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B2" s="9">
+        <v>180</v>
+      </c>
+      <c r="C2" s="10">
+        <v>0</v>
+      </c>
+      <c r="D2" s="10">
+        <v>0</v>
+      </c>
+      <c r="E2" s="10">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B3" s="9">
+        <v>180</v>
+      </c>
+      <c r="C3" s="10">
+        <v>0</v>
+      </c>
+      <c r="D3" s="10">
+        <v>0</v>
+      </c>
+      <c r="E3" s="10">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B4" s="9">
+        <v>180</v>
+      </c>
+      <c r="C4" s="10">
+        <v>0</v>
+      </c>
+      <c r="D4" s="10">
+        <v>0</v>
+      </c>
+      <c r="E4" s="10">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B7" s="10">
+        <v>22</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B8" s="10">
+        <v>9</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B9" s="10">
+        <v>5</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B10" s="10">
+        <v>5</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B11" s="10">
+        <v>3</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B12" s="10">
+        <v>32</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B13" s="10">
+        <v>30</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B14" s="10">
+        <v>28</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B15" s="10">
+        <v>26</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>946</v>
+      </c>
+      <c r="B16" s="10">
+        <v>20</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B17" s="15">
+        <v>180</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -2980,7 +6526,7 @@
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="46" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
     <col min="9" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2989,7 +6535,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2997,7 +6543,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3035,1026 +6581,1026 @@
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>14</v>
+        <v>284</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>15</v>
+        <v>285</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>16</v>
+        <v>286</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>17</v>
+        <v>287</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>19</v>
+        <v>288</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>21</v>
+        <v>288</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>22</v>
+        <v>289</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>23</v>
+        <v>290</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>24</v>
+        <v>291</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>25</v>
+        <v>292</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>26</v>
+        <v>293</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>21</v>
+        <v>293</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>27</v>
+        <v>294</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>28</v>
+        <v>295</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>29</v>
+        <v>296</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>30</v>
+        <v>297</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>31</v>
+        <v>298</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>32</v>
+        <v>299</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>21</v>
+        <v>299</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>33</v>
+        <v>300</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>34</v>
+        <v>301</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>35</v>
+        <v>302</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>36</v>
+        <v>303</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>37</v>
+        <v>304</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>38</v>
+        <v>305</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>21</v>
+        <v>305</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>39</v>
+        <v>306</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>40</v>
+        <v>307</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>41</v>
+        <v>308</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>42</v>
+        <v>309</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>43</v>
+        <v>310</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>44</v>
+        <v>311</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>21</v>
+        <v>311</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>46</v>
+        <v>312</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>47</v>
+        <v>313</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>48</v>
+        <v>314</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>49</v>
+        <v>315</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>50</v>
+        <v>316</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>51</v>
+        <v>317</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>21</v>
+        <v>317</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>52</v>
+        <v>318</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>53</v>
+        <v>319</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>54</v>
+        <v>320</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>55</v>
+        <v>321</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>56</v>
+        <v>322</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>57</v>
+        <v>323</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>21</v>
+        <v>323</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>59</v>
+        <v>324</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>60</v>
+        <v>325</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>62</v>
+        <v>326</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>63</v>
+        <v>327</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>64</v>
+        <v>328</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>21</v>
+        <v>328</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>65</v>
+        <v>329</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>66</v>
+        <v>330</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>67</v>
+        <v>331</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>68</v>
+        <v>332</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>69</v>
+        <v>333</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>21</v>
+        <v>333</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" ht="52" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>70</v>
+        <v>334</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>71</v>
+        <v>335</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>72</v>
+        <v>336</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>73</v>
+        <v>337</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>75</v>
+        <v>338</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>21</v>
+        <v>338</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>76</v>
+        <v>339</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>77</v>
+        <v>340</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>78</v>
+        <v>341</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>79</v>
+        <v>342</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>80</v>
+        <v>343</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>81</v>
+        <v>344</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>21</v>
+        <v>344</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>83</v>
+        <v>346</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>84</v>
+        <v>347</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>85</v>
+        <v>348</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>86</v>
+        <v>349</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>87</v>
+        <v>350</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>21</v>
+        <v>350</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>88</v>
+        <v>351</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>89</v>
+        <v>352</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>90</v>
+        <v>353</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>91</v>
+        <v>354</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>92</v>
+        <v>355</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>93</v>
+        <v>356</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>21</v>
+        <v>356</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>94</v>
+        <v>357</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>95</v>
+        <v>358</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>96</v>
+        <v>359</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>97</v>
+        <v>360</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>98</v>
+        <v>361</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>99</v>
+        <v>362</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>21</v>
+        <v>362</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>100</v>
+        <v>363</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>101</v>
+        <v>364</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>102</v>
+        <v>365</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>103</v>
+        <v>366</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>104</v>
+        <v>367</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>105</v>
+        <v>368</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>21</v>
+        <v>368</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>106</v>
+        <v>369</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>107</v>
+        <v>370</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>108</v>
+        <v>371</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>109</v>
+        <v>372</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>110</v>
+        <v>373</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>111</v>
+        <v>374</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>21</v>
+        <v>374</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>112</v>
+        <v>375</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>113</v>
+        <v>376</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>114</v>
+        <v>377</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>115</v>
+        <v>378</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>116</v>
+        <v>379</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>117</v>
+        <v>380</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>21</v>
+        <v>380</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>118</v>
+        <v>381</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>119</v>
+        <v>382</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>120</v>
+        <v>383</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>121</v>
+        <v>384</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>122</v>
+        <v>385</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>123</v>
+        <v>386</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>21</v>
+        <v>386</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>124</v>
+        <v>387</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>125</v>
+        <v>388</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>126</v>
+        <v>389</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>127</v>
+        <v>390</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>128</v>
+        <v>391</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>129</v>
+        <v>392</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>21</v>
+        <v>392</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>130</v>
+        <v>393</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>131</v>
+        <v>394</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>132</v>
+        <v>395</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>133</v>
+        <v>396</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>134</v>
+        <v>397</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>135</v>
+        <v>398</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>21</v>
+        <v>398</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>136</v>
+        <v>399</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>137</v>
+        <v>400</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>138</v>
+        <v>401</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>139</v>
+        <v>402</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>140</v>
+        <v>403</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>141</v>
+        <v>404</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>21</v>
+        <v>404</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" ht="52" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>142</v>
+        <v>405</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>143</v>
+        <v>406</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>144</v>
+        <v>407</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>145</v>
+        <v>408</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>146</v>
+        <v>409</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>147</v>
+        <v>410</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>21</v>
+        <v>410</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>148</v>
+        <v>411</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>149</v>
+        <v>412</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>150</v>
+        <v>413</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>151</v>
+        <v>414</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>152</v>
+        <v>415</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>153</v>
+        <v>416</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>21</v>
+        <v>416</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>154</v>
+        <v>417</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>155</v>
+        <v>418</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>156</v>
+        <v>419</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>157</v>
+        <v>420</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>158</v>
+        <v>421</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>159</v>
+        <v>422</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>21</v>
+        <v>422</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>160</v>
+        <v>423</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>161</v>
+        <v>424</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>162</v>
+        <v>425</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>163</v>
+        <v>426</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>164</v>
+        <v>427</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>165</v>
+        <v>428</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>21</v>
+        <v>428</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>166</v>
+        <v>429</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>167</v>
+        <v>430</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>168</v>
+        <v>431</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>169</v>
+        <v>432</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>170</v>
+        <v>433</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>21</v>
+        <v>433</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>171</v>
+        <v>434</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>172</v>
+        <v>435</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>173</v>
+        <v>436</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>174</v>
+        <v>437</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>175</v>
+        <v>438</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>21</v>
+        <v>438</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>176</v>
+        <v>439</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>177</v>
+        <v>440</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>178</v>
+        <v>441</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>179</v>
+        <v>442</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>180</v>
+        <v>443</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>181</v>
+        <v>444</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>21</v>
+        <v>444</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>182</v>
+        <v>445</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>183</v>
+        <v>446</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>184</v>
+        <v>447</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>185</v>
+        <v>448</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>186</v>
+        <v>449</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>187</v>
+        <v>450</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>21</v>
+        <v>450</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>188</v>
+        <v>451</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>189</v>
+        <v>452</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>190</v>
+        <v>453</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>191</v>
+        <v>454</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>192</v>
+        <v>455</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>193</v>
+        <v>456</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>21</v>
+        <v>456</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>194</v>
+        <v>457</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>195</v>
+        <v>458</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>196</v>
+        <v>459</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>197</v>
+        <v>460</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>198</v>
+        <v>461</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>199</v>
+        <v>462</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>21</v>
+        <v>462</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>200</v>
+        <v>463</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>201</v>
+        <v>464</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>202</v>
+        <v>465</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>203</v>
+        <v>466</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>204</v>
+        <v>467</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>205</v>
+        <v>468</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>21</v>
+        <v>468</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -4063,7 +7609,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -4075,7 +7621,7 @@
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="46" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
     <col min="9" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4084,7 +7630,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>206</v>
+        <v>469</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -4092,7 +7638,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>207</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4130,962 +7676,962 @@
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>208</v>
+        <v>471</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>209</v>
+        <v>472</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>210</v>
+        <v>473</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>211</v>
+        <v>474</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>212</v>
+        <v>475</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>21</v>
+        <v>475</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>213</v>
+        <v>476</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>214</v>
+        <v>477</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>215</v>
+        <v>478</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>216</v>
+        <v>479</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>217</v>
+        <v>480</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>218</v>
+        <v>481</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>21</v>
+        <v>481</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>219</v>
+        <v>482</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>220</v>
+        <v>483</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>221</v>
+        <v>484</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>222</v>
+        <v>485</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>223</v>
+        <v>486</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>224</v>
+        <v>487</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>21</v>
+        <v>487</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>225</v>
+        <v>488</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>226</v>
+        <v>489</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>227</v>
+        <v>490</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>228</v>
+        <v>491</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>229</v>
+        <v>492</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>230</v>
+        <v>493</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>21</v>
+        <v>493</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>231</v>
+        <v>494</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>232</v>
+        <v>495</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>233</v>
+        <v>496</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>234</v>
+        <v>497</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>235</v>
+        <v>498</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>236</v>
+        <v>499</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>21</v>
+        <v>499</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>237</v>
+        <v>500</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>238</v>
+        <v>501</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>239</v>
+        <v>502</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>240</v>
+        <v>503</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>241</v>
+        <v>504</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>242</v>
+        <v>505</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>21</v>
+        <v>505</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>243</v>
+        <v>506</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>244</v>
+        <v>507</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>245</v>
+        <v>508</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>246</v>
+        <v>509</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>247</v>
+        <v>510</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>242</v>
+        <v>505</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>21</v>
+        <v>505</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>248</v>
+        <v>511</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>249</v>
+        <v>512</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>250</v>
+        <v>513</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>251</v>
+        <v>514</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>252</v>
+        <v>515</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>253</v>
+        <v>516</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>21</v>
+        <v>516</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>254</v>
+        <v>517</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>255</v>
+        <v>518</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>256</v>
+        <v>519</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>257</v>
+        <v>520</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>258</v>
+        <v>521</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>253</v>
+        <v>516</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>21</v>
+        <v>516</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>259</v>
+        <v>522</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>260</v>
+        <v>523</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>261</v>
+        <v>524</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>262</v>
+        <v>525</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>263</v>
+        <v>526</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>264</v>
+        <v>527</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>21</v>
+        <v>527</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>265</v>
+        <v>528</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>266</v>
+        <v>529</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>267</v>
+        <v>530</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>268</v>
+        <v>531</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>269</v>
+        <v>532</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>270</v>
+        <v>533</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>21</v>
+        <v>533</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>271</v>
+        <v>534</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>272</v>
+        <v>535</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>273</v>
+        <v>536</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>274</v>
+        <v>537</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>275</v>
+        <v>538</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>276</v>
+        <v>539</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>21</v>
+        <v>539</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>277</v>
+        <v>540</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>278</v>
+        <v>541</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>279</v>
+        <v>542</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>280</v>
+        <v>543</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>281</v>
+        <v>544</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>282</v>
+        <v>545</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>21</v>
+        <v>545</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>283</v>
+        <v>546</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>284</v>
+        <v>547</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>285</v>
+        <v>548</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>286</v>
+        <v>549</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>287</v>
+        <v>550</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>288</v>
+        <v>551</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>21</v>
+        <v>551</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>289</v>
+        <v>552</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>290</v>
+        <v>553</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>291</v>
+        <v>554</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>292</v>
+        <v>555</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>293</v>
+        <v>556</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>294</v>
+        <v>557</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>21</v>
+        <v>557</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>295</v>
+        <v>558</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>296</v>
+        <v>559</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>297</v>
+        <v>560</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>298</v>
+        <v>561</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>299</v>
+        <v>562</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>300</v>
+        <v>563</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>21</v>
+        <v>563</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>301</v>
+        <v>564</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>302</v>
+        <v>565</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>303</v>
+        <v>566</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>304</v>
+        <v>567</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>305</v>
+        <v>568</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>306</v>
+        <v>569</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>21</v>
+        <v>569</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>307</v>
+        <v>570</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>308</v>
+        <v>571</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>309</v>
+        <v>572</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>310</v>
+        <v>573</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>293</v>
+        <v>556</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>311</v>
+        <v>574</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>21</v>
+        <v>574</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" ht="52" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>312</v>
+        <v>575</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>313</v>
+        <v>576</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>314</v>
+        <v>577</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>315</v>
+        <v>578</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>316</v>
+        <v>579</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>317</v>
+        <v>580</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>21</v>
+        <v>580</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>318</v>
+        <v>581</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>319</v>
+        <v>582</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>320</v>
+        <v>583</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>321</v>
+        <v>584</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>322</v>
+        <v>585</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>323</v>
+        <v>586</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>21</v>
+        <v>586</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>324</v>
+        <v>587</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>325</v>
+        <v>588</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>326</v>
+        <v>589</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>327</v>
+        <v>590</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>328</v>
+        <v>591</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>329</v>
+        <v>592</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>21</v>
+        <v>592</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>330</v>
+        <v>593</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>331</v>
+        <v>594</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>332</v>
+        <v>595</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>333</v>
+        <v>596</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>334</v>
+        <v>597</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>335</v>
+        <v>598</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>21</v>
+        <v>598</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>336</v>
+        <v>599</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>337</v>
+        <v>600</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>338</v>
+        <v>601</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>339</v>
+        <v>602</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>340</v>
+        <v>603</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>21</v>
+        <v>603</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>341</v>
+        <v>604</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>342</v>
+        <v>605</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>343</v>
+        <v>606</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>344</v>
+        <v>607</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>345</v>
+        <v>608</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>21</v>
+        <v>608</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>346</v>
+        <v>609</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>347</v>
+        <v>610</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>348</v>
+        <v>611</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>349</v>
+        <v>612</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>350</v>
+        <v>613</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>21</v>
+        <v>613</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>351</v>
+        <v>614</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>352</v>
+        <v>615</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>353</v>
+        <v>616</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>354</v>
+        <v>617</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>355</v>
+        <v>618</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>21</v>
+        <v>618</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>356</v>
+        <v>619</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>357</v>
+        <v>620</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>358</v>
+        <v>621</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>359</v>
+        <v>622</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>360</v>
+        <v>623</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>361</v>
+        <v>624</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>21</v>
+        <v>624</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>362</v>
+        <v>625</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>363</v>
+        <v>626</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>364</v>
+        <v>627</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>365</v>
+        <v>628</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>366</v>
+        <v>629</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>367</v>
+        <v>630</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>21</v>
+        <v>630</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>368</v>
+        <v>631</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>369</v>
+        <v>632</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>370</v>
+        <v>633</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>371</v>
+        <v>634</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>372</v>
+        <v>635</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>373</v>
+        <v>636</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>21</v>
+        <v>636</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>374</v>
+        <v>637</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>375</v>
+        <v>638</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>376</v>
+        <v>639</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>377</v>
+        <v>640</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>378</v>
+        <v>641</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>379</v>
+        <v>642</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>21</v>
+        <v>642</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -5094,7 +8640,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -5106,7 +8652,7 @@
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="46" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
     <col min="9" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5115,7 +8661,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>380</v>
+        <v>643</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -5123,7 +8669,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>381</v>
+        <v>644</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5161,898 +8707,898 @@
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>382</v>
+        <v>645</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>383</v>
+        <v>646</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>384</v>
+        <v>647</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>385</v>
+        <v>648</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>386</v>
+        <v>649</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>21</v>
+        <v>649</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>387</v>
+        <v>650</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>388</v>
+        <v>651</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>389</v>
+        <v>652</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>390</v>
+        <v>653</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>391</v>
+        <v>654</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>21</v>
+        <v>654</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>392</v>
+        <v>655</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>393</v>
+        <v>656</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>394</v>
+        <v>657</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>395</v>
+        <v>658</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>396</v>
+        <v>659</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>21</v>
+        <v>659</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>397</v>
+        <v>660</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>398</v>
+        <v>661</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>399</v>
+        <v>662</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>400</v>
+        <v>663</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>401</v>
+        <v>664</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>402</v>
+        <v>665</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>21</v>
+        <v>665</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>403</v>
+        <v>666</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>404</v>
+        <v>667</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>405</v>
+        <v>668</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>406</v>
+        <v>669</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>407</v>
+        <v>670</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>408</v>
+        <v>671</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>21</v>
+        <v>671</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>409</v>
+        <v>672</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>410</v>
+        <v>673</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>411</v>
+        <v>674</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>412</v>
+        <v>675</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>413</v>
+        <v>676</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>21</v>
+        <v>676</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>414</v>
+        <v>677</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>415</v>
+        <v>678</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>416</v>
+        <v>679</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>417</v>
+        <v>680</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>418</v>
+        <v>681</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>419</v>
+        <v>682</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>21</v>
+        <v>682</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>420</v>
+        <v>683</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>421</v>
+        <v>684</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>422</v>
+        <v>685</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>423</v>
+        <v>686</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>424</v>
+        <v>687</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>21</v>
+        <v>687</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>425</v>
+        <v>688</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>426</v>
+        <v>689</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>427</v>
+        <v>690</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>428</v>
+        <v>691</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>429</v>
+        <v>692</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>430</v>
+        <v>693</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>21</v>
+        <v>693</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>431</v>
+        <v>694</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>432</v>
+        <v>695</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>433</v>
+        <v>696</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>434</v>
+        <v>697</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>37</v>
+        <v>304</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>435</v>
+        <v>698</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>21</v>
+        <v>698</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>436</v>
+        <v>699</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>437</v>
+        <v>700</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>438</v>
+        <v>701</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>439</v>
+        <v>702</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>440</v>
+        <v>703</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>441</v>
+        <v>704</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>21</v>
+        <v>704</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>442</v>
+        <v>705</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>443</v>
+        <v>706</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>444</v>
+        <v>707</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>445</v>
+        <v>708</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>446</v>
+        <v>709</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>447</v>
+        <v>710</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>21</v>
+        <v>710</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>448</v>
+        <v>711</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>449</v>
+        <v>712</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>450</v>
+        <v>713</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>451</v>
+        <v>714</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>452</v>
+        <v>715</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>453</v>
+        <v>716</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>21</v>
+        <v>716</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>454</v>
+        <v>717</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>455</v>
+        <v>718</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>456</v>
+        <v>719</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>457</v>
+        <v>720</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>458</v>
+        <v>721</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>459</v>
+        <v>722</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>21</v>
+        <v>722</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>460</v>
+        <v>723</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>461</v>
+        <v>724</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>462</v>
+        <v>725</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>463</v>
+        <v>726</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>464</v>
+        <v>727</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>465</v>
+        <v>728</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>21</v>
+        <v>728</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>466</v>
+        <v>729</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>467</v>
+        <v>730</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>468</v>
+        <v>731</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>469</v>
+        <v>732</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>470</v>
+        <v>733</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>471</v>
+        <v>734</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>21</v>
+        <v>734</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>472</v>
+        <v>735</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>473</v>
+        <v>736</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>474</v>
+        <v>737</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>475</v>
+        <v>738</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>476</v>
+        <v>739</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>477</v>
+        <v>740</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>21</v>
+        <v>740</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>478</v>
+        <v>741</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>479</v>
+        <v>742</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>480</v>
+        <v>743</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>481</v>
+        <v>744</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>482</v>
+        <v>745</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>483</v>
+        <v>746</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>21</v>
+        <v>746</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>484</v>
+        <v>747</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>485</v>
+        <v>748</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>486</v>
+        <v>749</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>487</v>
+        <v>750</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>488</v>
+        <v>751</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>21</v>
+        <v>751</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>489</v>
+        <v>752</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>490</v>
+        <v>753</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>491</v>
+        <v>754</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>492</v>
+        <v>755</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>493</v>
+        <v>756</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>21</v>
+        <v>756</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>494</v>
+        <v>757</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>495</v>
+        <v>758</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>496</v>
+        <v>759</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>497</v>
+        <v>760</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>498</v>
+        <v>761</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>21</v>
+        <v>761</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>499</v>
+        <v>762</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>500</v>
+        <v>763</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>501</v>
+        <v>764</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>502</v>
+        <v>765</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>503</v>
+        <v>766</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>21</v>
+        <v>766</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>504</v>
+        <v>767</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>505</v>
+        <v>768</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>506</v>
+        <v>769</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>507</v>
+        <v>770</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>508</v>
+        <v>771</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>21</v>
+        <v>771</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>509</v>
+        <v>772</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>510</v>
+        <v>773</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>511</v>
+        <v>774</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>512</v>
+        <v>775</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>513</v>
+        <v>776</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>21</v>
+        <v>776</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>514</v>
+        <v>777</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>515</v>
+        <v>778</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>516</v>
+        <v>779</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>517</v>
+        <v>780</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>518</v>
+        <v>781</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>519</v>
+        <v>782</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>21</v>
+        <v>782</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>520</v>
+        <v>783</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>521</v>
+        <v>784</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>522</v>
+        <v>785</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>523</v>
+        <v>786</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>186</v>
+        <v>449</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>524</v>
+        <v>787</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>21</v>
+        <v>787</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>525</v>
+        <v>788</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>526</v>
+        <v>789</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>527</v>
+        <v>790</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>528</v>
+        <v>791</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>529</v>
+        <v>792</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>530</v>
+        <v>793</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>21</v>
+        <v>793</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>531</v>
+        <v>794</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>532</v>
+        <v>795</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>533</v>
+        <v>796</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>534</v>
+        <v>797</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>535</v>
+        <v>798</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>536</v>
+        <v>799</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>21</v>
+        <v>799</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -6061,7 +9607,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -6073,7 +9619,7 @@
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="46" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
     <col min="9" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6082,7 +9628,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>537</v>
+        <v>800</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -6090,7 +9636,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>538</v>
+        <v>801</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6128,1686 +9674,834 @@
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>539</v>
+        <v>802</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>540</v>
+        <v>803</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>541</v>
+        <v>804</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>542</v>
+        <v>805</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>543</v>
+        <v>806</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>21</v>
+        <v>806</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>544</v>
+        <v>807</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>545</v>
+        <v>808</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>546</v>
+        <v>809</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>547</v>
+        <v>810</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>548</v>
+        <v>811</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>549</v>
+        <v>812</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>21</v>
+        <v>812</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>550</v>
+        <v>813</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>551</v>
+        <v>814</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>552</v>
+        <v>815</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>553</v>
+        <v>816</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>554</v>
+        <v>817</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>555</v>
+        <v>818</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>21</v>
+        <v>818</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>556</v>
+        <v>819</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>557</v>
+        <v>820</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>558</v>
+        <v>821</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>559</v>
+        <v>822</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>560</v>
+        <v>823</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>561</v>
+        <v>824</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>21</v>
+        <v>824</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>562</v>
+        <v>825</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>563</v>
+        <v>826</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>564</v>
+        <v>827</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>565</v>
+        <v>828</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>566</v>
+        <v>829</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>567</v>
+        <v>830</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>21</v>
+        <v>830</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>568</v>
+        <v>831</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>569</v>
+        <v>832</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>570</v>
+        <v>833</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>571</v>
+        <v>834</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>572</v>
+        <v>835</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>573</v>
+        <v>836</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>21</v>
+        <v>836</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>574</v>
+        <v>837</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>575</v>
+        <v>838</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>576</v>
+        <v>839</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>577</v>
+        <v>840</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>578</v>
+        <v>841</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>579</v>
+        <v>842</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>21</v>
+        <v>842</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>580</v>
+        <v>843</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>581</v>
+        <v>844</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>582</v>
+        <v>845</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>583</v>
+        <v>846</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>584</v>
+        <v>847</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>585</v>
+        <v>848</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>21</v>
+        <v>848</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>586</v>
+        <v>849</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>587</v>
+        <v>850</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>588</v>
+        <v>851</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>589</v>
+        <v>852</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>590</v>
+        <v>853</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>591</v>
+        <v>854</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>21</v>
+        <v>854</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>592</v>
+        <v>855</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>593</v>
+        <v>856</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>594</v>
+        <v>857</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>595</v>
+        <v>858</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>554</v>
+        <v>817</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>596</v>
+        <v>859</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>21</v>
+        <v>859</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>597</v>
+        <v>860</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>598</v>
+        <v>861</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>599</v>
+        <v>862</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>600</v>
+        <v>863</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>601</v>
+        <v>864</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>602</v>
+        <v>865</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>21</v>
+        <v>865</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>603</v>
+        <v>866</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>604</v>
+        <v>867</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>605</v>
+        <v>868</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>606</v>
+        <v>869</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>607</v>
+        <v>870</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>21</v>
+        <v>870</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>608</v>
+        <v>871</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>609</v>
+        <v>872</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>610</v>
+        <v>873</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>611</v>
+        <v>874</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>554</v>
+        <v>817</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>612</v>
+        <v>875</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>21</v>
+        <v>875</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>613</v>
+        <v>876</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>614</v>
+        <v>877</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>615</v>
+        <v>878</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>616</v>
+        <v>879</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>601</v>
+        <v>864</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>617</v>
+        <v>880</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>21</v>
+        <v>880</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>618</v>
+        <v>881</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>619</v>
+        <v>882</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>620</v>
+        <v>883</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>621</v>
+        <v>884</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>554</v>
+        <v>817</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>622</v>
+        <v>885</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>21</v>
+        <v>885</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>623</v>
+        <v>886</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>624</v>
+        <v>887</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>625</v>
+        <v>888</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>626</v>
+        <v>889</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>627</v>
+        <v>890</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>21</v>
+        <v>890</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>628</v>
+        <v>891</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>629</v>
+        <v>892</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>630</v>
+        <v>893</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>631</v>
+        <v>894</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>632</v>
+        <v>895</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>633</v>
+        <v>896</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>21</v>
+        <v>896</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>634</v>
+        <v>897</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>635</v>
+        <v>898</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>636</v>
+        <v>899</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>637</v>
+        <v>900</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>554</v>
+        <v>817</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>638</v>
+        <v>901</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>21</v>
+        <v>901</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>639</v>
+        <v>902</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>640</v>
+        <v>903</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>641</v>
+        <v>904</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>642</v>
+        <v>905</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>643</v>
+        <v>906</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>21</v>
+        <v>906</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>644</v>
+        <v>907</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>645</v>
+        <v>908</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>646</v>
+        <v>909</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>647</v>
+        <v>910</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>554</v>
+        <v>817</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>648</v>
+        <v>911</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>21</v>
+        <v>911</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>649</v>
+        <v>912</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>650</v>
+        <v>913</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>651</v>
+        <v>914</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>652</v>
+        <v>915</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>653</v>
+        <v>916</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>654</v>
+        <v>917</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>21</v>
+        <v>917</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>655</v>
+        <v>918</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>656</v>
+        <v>919</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>657</v>
+        <v>920</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>658</v>
+        <v>921</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>659</v>
+        <v>922</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>21</v>
+        <v>922</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>660</v>
+        <v>923</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>661</v>
+        <v>924</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>662</v>
+        <v>925</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>663</v>
+        <v>926</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>664</v>
+        <v>927</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>665</v>
+        <v>928</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>21</v>
+        <v>928</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>666</v>
+        <v>929</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>667</v>
+        <v>930</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>668</v>
+        <v>931</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>669</v>
+        <v>932</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>186</v>
+        <v>449</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>670</v>
+        <v>933</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>21</v>
+        <v>933</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" ht="38" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>671</v>
+        <v>934</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>672</v>
+        <v>935</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>673</v>
+        <v>936</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>674</v>
+        <v>937</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>675</v>
+        <v>938</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>676</v>
+        <v>939</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>21</v>
+        <v>939</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>677</v>
+        <v>940</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>678</v>
+        <v>941</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>679</v>
+        <v>942</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>680</v>
+        <v>943</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>681</v>
+        <v>944</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>682</v>
+        <v>945</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>21</v>
+        <v>945</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J24"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="38" customWidth="1"/>
-    <col min="4" max="4" width="46" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="46" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="10" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>685</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>686</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>687</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>688</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>689</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>690</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>691</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>692</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>693</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>694</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>695</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>696</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>697</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>698</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>699</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>700</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>701</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>702</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>703</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>704</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>705</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>706</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>707</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>708</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>709</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>710</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>711</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>712</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>713</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>714</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>715</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>716</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>717</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>718</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>719</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>720</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>722</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>723</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>724</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>725</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>726</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>727</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>728</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>729</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>730</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>731</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>732</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>733</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>734</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>735</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>736</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>737</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>738</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>739</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>740</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>741</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>707</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>742</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>743</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>744</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>745</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>746</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>747</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>749</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>750</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>751</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>707</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>752</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>753</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>755</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>756</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>757</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>759</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>760</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>761</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>756</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>762</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>763</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>764</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>765</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>766</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>767</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>768</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>769</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>770</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>771</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>772</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>773</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>774</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>775</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>776</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>777</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>778</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>779</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>780</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>781</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>782</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>783</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>784</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>785</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>786</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>787</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>788</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>789</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>790</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>791</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>792</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>793</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>794</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>795</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>796</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>797</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>798</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>799</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="5" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>800</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>801</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>802</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>804</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0</v>
-      </c>
-      <c r="E2" s="8">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>805</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0</v>
-      </c>
-      <c r="E3" s="8">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>806</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0</v>
-      </c>
-      <c r="E4" s="8">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>807</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>809</v>
-      </c>
-      <c r="B7" s="8">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>810</v>
-      </c>
-      <c r="B8" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>380</v>
-      </c>
-      <c r="B9" s="8">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>811</v>
-      </c>
-      <c r="B10" s="8">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>683</v>
-      </c>
-      <c r="B11" s="8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>812</v>
-      </c>
-      <c r="B12" s="13">
-        <v>136</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
